--- a/QA_Dashboard.xlsx
+++ b/QA_Dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\excel_tutorial\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{517148CC-BE0D-40BE-AAFF-F3960D8D81F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7752B79A-9BA7-4DAF-986C-A6CC8C61D476}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,6 +23,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Bug Tracker'!$A$1:$L$500</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Test Runs'!$A$1:$F$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'🎯 QA Dashboard'!$B$2:$X$93</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -3545,68 +3546,96 @@
     <xf numFmtId="49" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="21" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="21" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="21" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="17" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="17" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="17" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="21" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="21" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="21" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="50" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="1" fontId="50" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="1" fontId="50" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="52" fillId="20" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="1" fontId="50" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="52" fillId="20" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="21" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="16" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="20" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="50" fillId="17" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -3615,76 +3644,6 @@
     </xf>
     <xf numFmtId="0" fontId="50" fillId="21" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="19" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="19" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="19" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="16" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -3696,10 +3655,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="20" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -3834,79 +3789,6 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="20" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="20" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="20" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="60" fillId="39" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3916,13 +3798,132 @@
     <xf numFmtId="0" fontId="61" fillId="39" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="50" fillId="21" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="19" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="19" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="19" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="50" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="50" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="50" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="50" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="21" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="21" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="21" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="17" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="17" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="17" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="21" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="21" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="21" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7213,6 +7214,61 @@
               </c:ext>
             </c:extLst>
           </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:srgbClr val="1F4E79"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>'Chart Data'!$S$3:$S$10</c:f>
@@ -13019,10 +13075,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -13360,90 +13412,90 @@
     </row>
     <row r="2" spans="1:25" ht="32.25" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="72"/>
-      <c r="B2" s="185" t="s">
+      <c r="B2" s="175" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="186"/>
-      <c r="D2" s="186"/>
-      <c r="E2" s="186"/>
-      <c r="F2" s="186"/>
-      <c r="G2" s="186"/>
-      <c r="H2" s="186"/>
-      <c r="I2" s="186"/>
-      <c r="J2" s="186"/>
-      <c r="K2" s="186"/>
-      <c r="L2" s="186"/>
-      <c r="M2" s="186"/>
-      <c r="N2" s="186"/>
-      <c r="O2" s="186"/>
-      <c r="P2" s="186"/>
-      <c r="Q2" s="186"/>
-      <c r="R2" s="186"/>
-      <c r="S2" s="186"/>
-      <c r="T2" s="186"/>
-      <c r="U2" s="186"/>
-      <c r="V2" s="186"/>
-      <c r="W2" s="186"/>
-      <c r="X2" s="187"/>
+      <c r="C2" s="176"/>
+      <c r="D2" s="176"/>
+      <c r="E2" s="176"/>
+      <c r="F2" s="176"/>
+      <c r="G2" s="176"/>
+      <c r="H2" s="176"/>
+      <c r="I2" s="176"/>
+      <c r="J2" s="176"/>
+      <c r="K2" s="176"/>
+      <c r="L2" s="176"/>
+      <c r="M2" s="176"/>
+      <c r="N2" s="176"/>
+      <c r="O2" s="176"/>
+      <c r="P2" s="176"/>
+      <c r="Q2" s="176"/>
+      <c r="R2" s="176"/>
+      <c r="S2" s="176"/>
+      <c r="T2" s="176"/>
+      <c r="U2" s="176"/>
+      <c r="V2" s="176"/>
+      <c r="W2" s="176"/>
+      <c r="X2" s="177"/>
       <c r="Y2" s="72"/>
     </row>
     <row r="3" spans="1:25" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A3" s="72"/>
-      <c r="B3" s="245" t="s">
+      <c r="B3" s="214" t="s">
         <v>586</v>
       </c>
-      <c r="C3" s="246"/>
-      <c r="D3" s="246"/>
-      <c r="E3" s="246"/>
-      <c r="F3" s="246"/>
-      <c r="G3" s="246"/>
-      <c r="H3" s="246"/>
-      <c r="I3" s="246"/>
-      <c r="J3" s="246"/>
-      <c r="K3" s="246"/>
-      <c r="L3" s="246"/>
-      <c r="M3" s="246"/>
-      <c r="N3" s="246"/>
-      <c r="O3" s="246"/>
-      <c r="P3" s="246"/>
-      <c r="Q3" s="246"/>
-      <c r="R3" s="246"/>
-      <c r="S3" s="246"/>
-      <c r="T3" s="246"/>
-      <c r="U3" s="246"/>
-      <c r="V3" s="246"/>
-      <c r="W3" s="246"/>
-      <c r="X3" s="247"/>
+      <c r="C3" s="215"/>
+      <c r="D3" s="215"/>
+      <c r="E3" s="215"/>
+      <c r="F3" s="215"/>
+      <c r="G3" s="215"/>
+      <c r="H3" s="215"/>
+      <c r="I3" s="215"/>
+      <c r="J3" s="215"/>
+      <c r="K3" s="215"/>
+      <c r="L3" s="215"/>
+      <c r="M3" s="215"/>
+      <c r="N3" s="215"/>
+      <c r="O3" s="215"/>
+      <c r="P3" s="215"/>
+      <c r="Q3" s="215"/>
+      <c r="R3" s="215"/>
+      <c r="S3" s="215"/>
+      <c r="T3" s="215"/>
+      <c r="U3" s="215"/>
+      <c r="V3" s="215"/>
+      <c r="W3" s="215"/>
+      <c r="X3" s="216"/>
       <c r="Y3" s="72"/>
     </row>
     <row r="4" spans="1:25" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="72"/>
-      <c r="B4" s="209" t="str">
+      <c r="B4" s="198" t="str">
         <f ca="1">"Sprint 8 (Current)   |   Total Bugs: "&amp;COUNTA('Bug Tracker'!A:A)-1&amp;"   |   Open: "&amp;COUNTIFS('Bug Tracker'!D:D,"Open")+COUNTIFS('Bug Tracker'!D:D,"In Progress")+COUNTIFS('Bug Tracker'!D:D,"Reopened")&amp;"   |   Critical Open: "&amp;COUNTIFS('Bug Tracker'!C:C,"Critical",'Bug Tracker'!D:D,"Open")+COUNTIFS('Bug Tracker'!C:C,"Critical",'Bug Tracker'!D:D,"In Progress")+COUNTIFS('Bug Tracker'!C:C,"Critical",'Bug Tracker'!D:D,"Reopened")&amp;"   |   Report Date: "&amp;TEXT(TODAY(),"mmmm d, yyyy")</f>
         <v>Sprint 8 (Current)   |   Total Bugs: 201   |   Open: 57   |   Critical Open: 2   |   Report Date: May 23, 2026</v>
       </c>
-      <c r="C4" s="210"/>
-      <c r="D4" s="210"/>
-      <c r="E4" s="210"/>
-      <c r="F4" s="210"/>
-      <c r="G4" s="210"/>
-      <c r="H4" s="210"/>
-      <c r="I4" s="210"/>
-      <c r="J4" s="210"/>
-      <c r="K4" s="210"/>
-      <c r="L4" s="210"/>
-      <c r="M4" s="210"/>
-      <c r="N4" s="210"/>
-      <c r="O4" s="210"/>
-      <c r="P4" s="210"/>
-      <c r="Q4" s="210"/>
-      <c r="R4" s="210"/>
-      <c r="S4" s="210"/>
-      <c r="T4" s="210"/>
-      <c r="U4" s="210"/>
-      <c r="V4" s="210"/>
-      <c r="W4" s="210"/>
-      <c r="X4" s="211"/>
+      <c r="C4" s="199"/>
+      <c r="D4" s="199"/>
+      <c r="E4" s="199"/>
+      <c r="F4" s="199"/>
+      <c r="G4" s="199"/>
+      <c r="H4" s="199"/>
+      <c r="I4" s="199"/>
+      <c r="J4" s="199"/>
+      <c r="K4" s="199"/>
+      <c r="L4" s="199"/>
+      <c r="M4" s="199"/>
+      <c r="N4" s="199"/>
+      <c r="O4" s="199"/>
+      <c r="P4" s="199"/>
+      <c r="Q4" s="199"/>
+      <c r="R4" s="199"/>
+      <c r="S4" s="199"/>
+      <c r="T4" s="199"/>
+      <c r="U4" s="199"/>
+      <c r="V4" s="199"/>
+      <c r="W4" s="199"/>
+      <c r="X4" s="200"/>
       <c r="Y4" s="72"/>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.25">
@@ -13475,164 +13527,164 @@
     </row>
     <row r="6" spans="1:25" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A6" s="72"/>
-      <c r="B6" s="189" t="s">
+      <c r="B6" s="178" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="190"/>
-      <c r="D6" s="190"/>
+      <c r="C6" s="179"/>
+      <c r="D6" s="179"/>
       <c r="E6" s="72"/>
-      <c r="F6" s="201" t="s">
+      <c r="F6" s="190" t="s">
         <v>2</v>
       </c>
-      <c r="G6" s="202"/>
-      <c r="H6" s="202"/>
+      <c r="G6" s="191"/>
+      <c r="H6" s="191"/>
       <c r="I6" s="72"/>
-      <c r="J6" s="163" t="s">
+      <c r="J6" s="218" t="s">
         <v>3</v>
       </c>
-      <c r="K6" s="164"/>
-      <c r="L6" s="164"/>
+      <c r="K6" s="219"/>
+      <c r="L6" s="219"/>
       <c r="M6" s="72"/>
-      <c r="N6" s="194" t="s">
+      <c r="N6" s="183" t="s">
         <v>4</v>
       </c>
-      <c r="O6" s="195"/>
-      <c r="P6" s="195"/>
+      <c r="O6" s="184"/>
+      <c r="P6" s="184"/>
       <c r="Q6" s="72"/>
-      <c r="R6" s="207" t="s">
+      <c r="R6" s="196" t="s">
         <v>5</v>
       </c>
-      <c r="S6" s="208"/>
-      <c r="T6" s="208"/>
+      <c r="S6" s="197"/>
+      <c r="T6" s="197"/>
       <c r="U6" s="72"/>
-      <c r="V6" s="169" t="s">
+      <c r="V6" s="220" t="s">
         <v>6</v>
       </c>
-      <c r="W6" s="170"/>
-      <c r="X6" s="171"/>
+      <c r="W6" s="221"/>
+      <c r="X6" s="222"/>
       <c r="Y6" s="72"/>
     </row>
     <row r="7" spans="1:25" ht="42" x14ac:dyDescent="0.65">
       <c r="A7" s="72"/>
-      <c r="B7" s="197">
+      <c r="B7" s="186">
         <f>COUNTA('Bug Tracker'!A:A)-1</f>
         <v>201</v>
       </c>
-      <c r="C7" s="198"/>
-      <c r="D7" s="198"/>
+      <c r="C7" s="187"/>
+      <c r="D7" s="187"/>
       <c r="E7" s="72"/>
-      <c r="F7" s="203">
+      <c r="F7" s="192">
         <f>COUNTIFS('Bug Tracker'!D:D,"Open")+COUNTIFS('Bug Tracker'!D:D,"In Progress")+COUNTIFS('Bug Tracker'!D:D,"Reopened")</f>
         <v>57</v>
       </c>
-      <c r="G7" s="204"/>
-      <c r="H7" s="204"/>
+      <c r="G7" s="193"/>
+      <c r="H7" s="193"/>
       <c r="I7" s="72"/>
-      <c r="J7" s="172" t="str">
+      <c r="J7" s="223" t="str">
         <f>TEXT(AVERAGE('Test Runs'!F2:F9)/100,"0.0%")</f>
         <v>79.6%</v>
       </c>
-      <c r="K7" s="173"/>
-      <c r="L7" s="173"/>
+      <c r="K7" s="224"/>
+      <c r="L7" s="224"/>
       <c r="M7" s="72"/>
-      <c r="N7" s="199">
+      <c r="N7" s="188">
         <f>COUNTIFS('Bug Tracker'!C:C,"Critical",'Bug Tracker'!D:D,"Open")+COUNTIFS('Bug Tracker'!C:C,"Critical",'Bug Tracker'!D:D,"In Progress")+COUNTIFS('Bug Tracker'!C:C,"Critical",'Bug Tracker'!D:D,"Reopened")</f>
         <v>2</v>
       </c>
-      <c r="O7" s="200"/>
-      <c r="P7" s="200"/>
+      <c r="O7" s="189"/>
+      <c r="P7" s="189"/>
       <c r="Q7" s="72"/>
-      <c r="R7" s="205" cm="1">
+      <c r="R7" s="194" cm="1">
         <f t="array" aca="1" ref="R7" ca="1">ROUND(SUMPRODUCT(('Bug Tracker'!J2:J201)*(('Bug Tracker'!D2:D201="Open")+('Bug Tracker'!D2:D201="In Progress")+('Bug Tracker'!D2:D201="Reopened")))/SUMPRODUCT(--((('Bug Tracker'!D2:D201="Open")+('Bug Tracker'!D2:D201="In Progress")+('Bug Tracker'!D2:D201="Reopened"))&gt;0)),1)</f>
         <v>129</v>
       </c>
-      <c r="S7" s="206"/>
-      <c r="T7" s="206"/>
+      <c r="S7" s="195"/>
+      <c r="T7" s="195"/>
       <c r="U7" s="72"/>
-      <c r="V7" s="191" t="str">
+      <c r="V7" s="180" t="str">
         <f>TEXT((COUNTIFS('Bug Tracker'!D:D,"Closed")+COUNTIFS('Bug Tracker'!D:D,"Fixed")+COUNTIFS('Bug Tracker'!D:D,"Verified"))/(COUNTA('Bug Tracker'!A:A)-1),"0.0%")</f>
         <v>71.6%</v>
       </c>
-      <c r="W7" s="192"/>
-      <c r="X7" s="193"/>
+      <c r="W7" s="181"/>
+      <c r="X7" s="182"/>
       <c r="Y7" s="72"/>
     </row>
     <row r="8" spans="1:25" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="72"/>
-      <c r="B8" s="212" t="s">
+      <c r="B8" s="201" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="213"/>
-      <c r="D8" s="213"/>
+      <c r="C8" s="202"/>
+      <c r="D8" s="202"/>
       <c r="E8" s="72"/>
-      <c r="F8" s="221" t="s">
+      <c r="F8" s="210" t="s">
         <v>485</v>
       </c>
-      <c r="G8" s="222"/>
-      <c r="H8" s="222"/>
+      <c r="G8" s="211"/>
+      <c r="H8" s="211"/>
       <c r="I8" s="72"/>
-      <c r="J8" s="235" t="s">
+      <c r="J8" s="167" t="s">
         <v>8</v>
       </c>
-      <c r="K8" s="236"/>
-      <c r="L8" s="236"/>
+      <c r="K8" s="168"/>
+      <c r="L8" s="168"/>
       <c r="M8" s="72"/>
-      <c r="N8" s="223" t="s">
+      <c r="N8" s="212" t="s">
         <v>486</v>
       </c>
-      <c r="O8" s="224"/>
-      <c r="P8" s="224"/>
+      <c r="O8" s="213"/>
+      <c r="P8" s="213"/>
       <c r="Q8" s="72"/>
-      <c r="R8" s="237" t="s">
+      <c r="R8" s="169" t="s">
         <v>9</v>
       </c>
-      <c r="S8" s="238"/>
-      <c r="T8" s="238"/>
+      <c r="S8" s="170"/>
+      <c r="T8" s="170"/>
       <c r="U8" s="72"/>
-      <c r="V8" s="227" t="s">
+      <c r="V8" s="156" t="s">
         <v>10</v>
       </c>
-      <c r="W8" s="228"/>
-      <c r="X8" s="229"/>
+      <c r="W8" s="157"/>
+      <c r="X8" s="158"/>
       <c r="Y8" s="72"/>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9" s="72"/>
-      <c r="B9" s="179" t="s">
+      <c r="B9" s="228" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="180"/>
-      <c r="D9" s="180"/>
+      <c r="C9" s="229"/>
+      <c r="D9" s="229"/>
       <c r="E9" s="72"/>
-      <c r="F9" s="183" t="s">
+      <c r="F9" s="232" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="184"/>
-      <c r="H9" s="184"/>
+      <c r="G9" s="233"/>
+      <c r="H9" s="233"/>
       <c r="I9" s="72"/>
-      <c r="J9" s="231" t="s">
+      <c r="J9" s="161" t="s">
         <v>11</v>
       </c>
-      <c r="K9" s="232"/>
-      <c r="L9" s="232"/>
+      <c r="K9" s="162"/>
+      <c r="L9" s="162"/>
       <c r="M9" s="72"/>
-      <c r="N9" s="181" t="s">
+      <c r="N9" s="230" t="s">
         <v>13</v>
       </c>
-      <c r="O9" s="182"/>
-      <c r="P9" s="182"/>
+      <c r="O9" s="231"/>
+      <c r="P9" s="231"/>
       <c r="Q9" s="72"/>
-      <c r="R9" s="233" t="s">
+      <c r="R9" s="165" t="s">
         <v>14</v>
       </c>
-      <c r="S9" s="234"/>
-      <c r="T9" s="234"/>
+      <c r="S9" s="166"/>
+      <c r="T9" s="166"/>
       <c r="U9" s="72"/>
-      <c r="V9" s="218" t="s">
+      <c r="V9" s="207" t="s">
         <v>15</v>
       </c>
-      <c r="W9" s="219"/>
-      <c r="X9" s="220"/>
+      <c r="W9" s="208"/>
+      <c r="X9" s="209"/>
       <c r="Y9" s="72"/>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.25">
@@ -13664,33 +13716,33 @@
     </row>
     <row r="11" spans="1:25" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A11" s="72"/>
-      <c r="B11" s="230" t="s">
+      <c r="B11" s="171" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="177"/>
-      <c r="D11" s="177"/>
-      <c r="E11" s="177"/>
-      <c r="F11" s="177"/>
-      <c r="G11" s="177"/>
-      <c r="H11" s="177"/>
-      <c r="I11" s="177"/>
-      <c r="J11" s="177"/>
-      <c r="K11" s="177"/>
-      <c r="L11" s="249" t="s">
+      <c r="C11" s="160"/>
+      <c r="D11" s="160"/>
+      <c r="E11" s="160"/>
+      <c r="F11" s="160"/>
+      <c r="G11" s="160"/>
+      <c r="H11" s="160"/>
+      <c r="I11" s="160"/>
+      <c r="J11" s="160"/>
+      <c r="K11" s="160"/>
+      <c r="L11" s="163" t="s">
         <v>17</v>
       </c>
-      <c r="M11" s="177"/>
-      <c r="N11" s="177"/>
-      <c r="O11" s="177"/>
-      <c r="P11" s="177"/>
-      <c r="Q11" s="177"/>
-      <c r="R11" s="177"/>
-      <c r="S11" s="177"/>
-      <c r="T11" s="177"/>
-      <c r="U11" s="177"/>
-      <c r="V11" s="177"/>
-      <c r="W11" s="177"/>
-      <c r="X11" s="178"/>
+      <c r="M11" s="160"/>
+      <c r="N11" s="160"/>
+      <c r="O11" s="160"/>
+      <c r="P11" s="160"/>
+      <c r="Q11" s="160"/>
+      <c r="R11" s="160"/>
+      <c r="S11" s="160"/>
+      <c r="T11" s="160"/>
+      <c r="U11" s="160"/>
+      <c r="V11" s="160"/>
+      <c r="W11" s="160"/>
+      <c r="X11" s="164"/>
       <c r="Y11" s="72"/>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.25">
@@ -14154,33 +14206,33 @@
     </row>
     <row r="29" spans="1:25" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A29" s="72"/>
-      <c r="B29" s="248" t="s">
+      <c r="B29" s="159" t="s">
         <v>588</v>
       </c>
-      <c r="C29" s="177"/>
-      <c r="D29" s="177"/>
-      <c r="E29" s="177"/>
-      <c r="F29" s="177"/>
-      <c r="G29" s="177"/>
-      <c r="H29" s="177"/>
-      <c r="I29" s="177"/>
-      <c r="J29" s="177"/>
-      <c r="K29" s="177"/>
-      <c r="L29" s="249" t="s">
+      <c r="C29" s="160"/>
+      <c r="D29" s="160"/>
+      <c r="E29" s="160"/>
+      <c r="F29" s="160"/>
+      <c r="G29" s="160"/>
+      <c r="H29" s="160"/>
+      <c r="I29" s="160"/>
+      <c r="J29" s="160"/>
+      <c r="K29" s="160"/>
+      <c r="L29" s="163" t="s">
         <v>18</v>
       </c>
-      <c r="M29" s="177"/>
-      <c r="N29" s="177"/>
-      <c r="O29" s="177"/>
-      <c r="P29" s="177"/>
-      <c r="Q29" s="177"/>
-      <c r="R29" s="177"/>
-      <c r="S29" s="177"/>
-      <c r="T29" s="177"/>
-      <c r="U29" s="177"/>
-      <c r="V29" s="177"/>
-      <c r="W29" s="177"/>
-      <c r="X29" s="178"/>
+      <c r="M29" s="160"/>
+      <c r="N29" s="160"/>
+      <c r="O29" s="160"/>
+      <c r="P29" s="160"/>
+      <c r="Q29" s="160"/>
+      <c r="R29" s="160"/>
+      <c r="S29" s="160"/>
+      <c r="T29" s="160"/>
+      <c r="U29" s="160"/>
+      <c r="V29" s="160"/>
+      <c r="W29" s="160"/>
+      <c r="X29" s="164"/>
       <c r="Y29" s="72"/>
     </row>
     <row r="30" spans="1:25" x14ac:dyDescent="0.25">
@@ -14671,33 +14723,33 @@
     </row>
     <row r="48" spans="1:25" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A48" s="72"/>
-      <c r="B48" s="248" t="s">
+      <c r="B48" s="159" t="s">
         <v>587</v>
       </c>
-      <c r="C48" s="177"/>
-      <c r="D48" s="177"/>
-      <c r="E48" s="177"/>
-      <c r="F48" s="177"/>
-      <c r="G48" s="177"/>
-      <c r="H48" s="177"/>
-      <c r="I48" s="177"/>
-      <c r="J48" s="177"/>
-      <c r="K48" s="177"/>
-      <c r="L48" s="249" t="s">
+      <c r="C48" s="160"/>
+      <c r="D48" s="160"/>
+      <c r="E48" s="160"/>
+      <c r="F48" s="160"/>
+      <c r="G48" s="160"/>
+      <c r="H48" s="160"/>
+      <c r="I48" s="160"/>
+      <c r="J48" s="160"/>
+      <c r="K48" s="160"/>
+      <c r="L48" s="163" t="s">
         <v>19</v>
       </c>
-      <c r="M48" s="177"/>
-      <c r="N48" s="177"/>
-      <c r="O48" s="177"/>
-      <c r="P48" s="177"/>
-      <c r="Q48" s="177"/>
-      <c r="R48" s="177"/>
-      <c r="S48" s="177"/>
-      <c r="T48" s="177"/>
-      <c r="U48" s="177"/>
-      <c r="V48" s="177"/>
-      <c r="W48" s="177"/>
-      <c r="X48" s="178"/>
+      <c r="M48" s="160"/>
+      <c r="N48" s="160"/>
+      <c r="O48" s="160"/>
+      <c r="P48" s="160"/>
+      <c r="Q48" s="160"/>
+      <c r="R48" s="160"/>
+      <c r="S48" s="160"/>
+      <c r="T48" s="160"/>
+      <c r="U48" s="160"/>
+      <c r="V48" s="160"/>
+      <c r="W48" s="160"/>
+      <c r="X48" s="164"/>
       <c r="Y48" s="72"/>
     </row>
     <row r="49" spans="1:25" x14ac:dyDescent="0.25">
@@ -15134,33 +15186,33 @@
     </row>
     <row r="65" spans="1:25" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="72"/>
-      <c r="B65" s="214" t="s">
+      <c r="B65" s="203" t="s">
         <v>488</v>
       </c>
-      <c r="C65" s="215"/>
-      <c r="D65" s="215"/>
-      <c r="E65" s="215"/>
-      <c r="F65" s="215"/>
-      <c r="G65" s="215"/>
-      <c r="H65" s="215"/>
-      <c r="I65" s="215"/>
-      <c r="J65" s="215"/>
-      <c r="K65" s="215"/>
-      <c r="L65" s="216" t="s">
+      <c r="C65" s="204"/>
+      <c r="D65" s="204"/>
+      <c r="E65" s="204"/>
+      <c r="F65" s="204"/>
+      <c r="G65" s="204"/>
+      <c r="H65" s="204"/>
+      <c r="I65" s="204"/>
+      <c r="J65" s="204"/>
+      <c r="K65" s="204"/>
+      <c r="L65" s="205" t="s">
         <v>489</v>
       </c>
-      <c r="M65" s="215"/>
-      <c r="N65" s="215"/>
-      <c r="O65" s="215"/>
-      <c r="P65" s="215"/>
-      <c r="Q65" s="215"/>
-      <c r="R65" s="215"/>
-      <c r="S65" s="215"/>
-      <c r="T65" s="215"/>
-      <c r="U65" s="215"/>
-      <c r="V65" s="215"/>
-      <c r="W65" s="215"/>
-      <c r="X65" s="217"/>
+      <c r="M65" s="204"/>
+      <c r="N65" s="204"/>
+      <c r="O65" s="204"/>
+      <c r="P65" s="204"/>
+      <c r="Q65" s="204"/>
+      <c r="R65" s="204"/>
+      <c r="S65" s="204"/>
+      <c r="T65" s="204"/>
+      <c r="U65" s="204"/>
+      <c r="V65" s="204"/>
+      <c r="W65" s="204"/>
+      <c r="X65" s="206"/>
       <c r="Y65" s="72"/>
     </row>
     <row r="66" spans="1:25" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -15597,72 +15649,72 @@
     </row>
     <row r="82" spans="1:25" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A82" s="72"/>
-      <c r="B82" s="174" t="s">
+      <c r="B82" s="225" t="s">
         <v>20</v>
       </c>
-      <c r="C82" s="175"/>
-      <c r="D82" s="175"/>
-      <c r="E82" s="175"/>
-      <c r="F82" s="175"/>
-      <c r="G82" s="175"/>
-      <c r="H82" s="175"/>
-      <c r="I82" s="175"/>
-      <c r="J82" s="175"/>
-      <c r="K82" s="175"/>
-      <c r="L82" s="175"/>
-      <c r="M82" s="175"/>
-      <c r="N82" s="175"/>
-      <c r="O82" s="175"/>
-      <c r="P82" s="175"/>
-      <c r="Q82" s="175"/>
-      <c r="R82" s="175"/>
-      <c r="S82" s="175"/>
-      <c r="T82" s="175"/>
-      <c r="U82" s="175"/>
-      <c r="V82" s="176"/>
-      <c r="W82" s="175"/>
-      <c r="X82" s="176"/>
+      <c r="C82" s="226"/>
+      <c r="D82" s="226"/>
+      <c r="E82" s="226"/>
+      <c r="F82" s="226"/>
+      <c r="G82" s="226"/>
+      <c r="H82" s="226"/>
+      <c r="I82" s="226"/>
+      <c r="J82" s="226"/>
+      <c r="K82" s="226"/>
+      <c r="L82" s="226"/>
+      <c r="M82" s="226"/>
+      <c r="N82" s="226"/>
+      <c r="O82" s="226"/>
+      <c r="P82" s="226"/>
+      <c r="Q82" s="226"/>
+      <c r="R82" s="226"/>
+      <c r="S82" s="226"/>
+      <c r="T82" s="226"/>
+      <c r="U82" s="226"/>
+      <c r="V82" s="227"/>
+      <c r="W82" s="226"/>
+      <c r="X82" s="227"/>
       <c r="Y82" s="72"/>
     </row>
     <row r="83" spans="1:25" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="72"/>
-      <c r="B83" s="239" t="s">
+      <c r="B83" s="172" t="s">
         <v>21</v>
       </c>
       <c r="C83" s="136"/>
-      <c r="D83" s="188" t="s">
+      <c r="D83" s="153" t="s">
         <v>22</v>
       </c>
-      <c r="E83" s="196"/>
-      <c r="F83" s="196"/>
-      <c r="G83" s="196"/>
-      <c r="H83" s="196"/>
-      <c r="I83" s="196"/>
+      <c r="E83" s="185"/>
+      <c r="F83" s="185"/>
+      <c r="G83" s="185"/>
+      <c r="H83" s="185"/>
+      <c r="I83" s="185"/>
       <c r="J83" s="137"/>
-      <c r="K83" s="188" t="s">
+      <c r="K83" s="153" t="s">
         <v>23</v>
       </c>
       <c r="L83" s="137"/>
-      <c r="M83" s="188" t="s">
+      <c r="M83" s="153" t="s">
         <v>24</v>
       </c>
       <c r="N83" s="137"/>
-      <c r="O83" s="188" t="s">
+      <c r="O83" s="153" t="s">
         <v>25</v>
       </c>
       <c r="P83" s="137"/>
-      <c r="Q83" s="188" t="s">
+      <c r="Q83" s="153" t="s">
         <v>26</v>
       </c>
       <c r="R83" s="137"/>
-      <c r="S83" s="188" t="s">
+      <c r="S83" s="153" t="s">
         <v>27</v>
       </c>
       <c r="T83" s="137"/>
-      <c r="U83" s="225" t="s">
+      <c r="U83" s="154" t="s">
         <v>28</v>
       </c>
-      <c r="V83" s="226"/>
+      <c r="V83" s="155"/>
       <c r="W83" s="73"/>
       <c r="X83" s="88"/>
       <c r="Y83" s="72"/>
@@ -15673,15 +15725,15 @@
         <v>29</v>
       </c>
       <c r="C84" s="106"/>
-      <c r="D84" s="165" t="str">
+      <c r="D84" s="173" t="str">
         <f>IF(B84="","",IFERROR(VLOOKUP(B84,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v>[User Mgmt] 500 error</v>
       </c>
-      <c r="E84" s="165"/>
-      <c r="F84" s="165"/>
-      <c r="G84" s="165"/>
-      <c r="H84" s="165"/>
-      <c r="I84" s="165"/>
+      <c r="E84" s="173"/>
+      <c r="F84" s="173"/>
+      <c r="G84" s="173"/>
+      <c r="H84" s="173"/>
+      <c r="I84" s="173"/>
       <c r="J84" s="90"/>
       <c r="K84" s="138" t="str">
         <f>IF(B84="","",IFERROR(VLOOKUP(B84,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -15708,11 +15760,11 @@
         <v>Sprint 7</v>
       </c>
       <c r="T84" s="91"/>
-      <c r="U84" s="167">
+      <c r="U84" s="151">
         <f ca="1">IF(B84="","",IFERROR(VLOOKUP(B84,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v>234</v>
       </c>
-      <c r="V84" s="168"/>
+      <c r="V84" s="152"/>
       <c r="W84" s="73"/>
       <c r="X84" s="88"/>
       <c r="Y84" s="72"/>
@@ -15723,15 +15775,15 @@
         <v>34</v>
       </c>
       <c r="C85" s="107"/>
-      <c r="D85" s="166" t="str">
+      <c r="D85" s="174" t="str">
         <f>IF(B85="","",IFERROR(VLOOKUP(B85,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v>[Export] Memory leak</v>
       </c>
-      <c r="E85" s="166"/>
-      <c r="F85" s="166"/>
-      <c r="G85" s="166"/>
-      <c r="H85" s="166"/>
-      <c r="I85" s="166"/>
+      <c r="E85" s="174"/>
+      <c r="F85" s="174"/>
+      <c r="G85" s="174"/>
+      <c r="H85" s="174"/>
+      <c r="I85" s="174"/>
       <c r="J85" s="93"/>
       <c r="K85" s="140" t="str">
         <f>IF(B85="","",IFERROR(VLOOKUP(B85,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -15758,11 +15810,11 @@
         <v>Sprint 7</v>
       </c>
       <c r="T85" s="94"/>
-      <c r="U85" s="167">
+      <c r="U85" s="151">
         <f ca="1">IF(B85="","",IFERROR(VLOOKUP(B85,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v>226</v>
       </c>
-      <c r="V85" s="168"/>
+      <c r="V85" s="152"/>
       <c r="W85" s="73"/>
       <c r="X85" s="88"/>
       <c r="Y85" s="72"/>
@@ -15773,15 +15825,15 @@
         <v>38</v>
       </c>
       <c r="C86" s="106"/>
-      <c r="D86" s="165" t="str">
+      <c r="D86" s="173" t="str">
         <f>IF(B86="","",IFERROR(VLOOKUP(B86,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v>[Dashboard] Missing validation</v>
       </c>
-      <c r="E86" s="165"/>
-      <c r="F86" s="165"/>
-      <c r="G86" s="165"/>
-      <c r="H86" s="165"/>
-      <c r="I86" s="165"/>
+      <c r="E86" s="173"/>
+      <c r="F86" s="173"/>
+      <c r="G86" s="173"/>
+      <c r="H86" s="173"/>
+      <c r="I86" s="173"/>
       <c r="J86" s="90"/>
       <c r="K86" s="138" t="str">
         <f>IF(B86="","",IFERROR(VLOOKUP(B86,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -15808,11 +15860,11 @@
         <v>Sprint 1</v>
       </c>
       <c r="T86" s="91"/>
-      <c r="U86" s="167">
+      <c r="U86" s="151">
         <f ca="1">IF(B86="","",IFERROR(VLOOKUP(B86,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v>188</v>
       </c>
-      <c r="V86" s="168"/>
+      <c r="V86" s="152"/>
       <c r="W86" s="73"/>
       <c r="X86" s="88"/>
       <c r="Y86" s="72"/>
@@ -15823,15 +15875,15 @@
         <v>40</v>
       </c>
       <c r="C87" s="107"/>
-      <c r="D87" s="166" t="str">
+      <c r="D87" s="174" t="str">
         <f>IF(B87="","",IFERROR(VLOOKUP(B87,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v>[Export] Missing validation</v>
       </c>
-      <c r="E87" s="166"/>
-      <c r="F87" s="166"/>
-      <c r="G87" s="166"/>
-      <c r="H87" s="166"/>
-      <c r="I87" s="166"/>
+      <c r="E87" s="174"/>
+      <c r="F87" s="174"/>
+      <c r="G87" s="174"/>
+      <c r="H87" s="174"/>
+      <c r="I87" s="174"/>
       <c r="J87" s="93"/>
       <c r="K87" s="140" t="str">
         <f>IF(B87="","",IFERROR(VLOOKUP(B87,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -15858,11 +15910,11 @@
         <v>Sprint 2</v>
       </c>
       <c r="T87" s="94"/>
-      <c r="U87" s="167">
+      <c r="U87" s="151">
         <f ca="1">IF(B87="","",IFERROR(VLOOKUP(B87,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v>178</v>
       </c>
-      <c r="V87" s="168"/>
+      <c r="V87" s="152"/>
       <c r="W87" s="73"/>
       <c r="X87" s="88"/>
       <c r="Y87" s="72"/>
@@ -15873,15 +15925,15 @@
         <v>43</v>
       </c>
       <c r="C88" s="106"/>
-      <c r="D88" s="165" t="str">
+      <c r="D88" s="173" t="str">
         <f>IF(B88="","",IFERROR(VLOOKUP(B88,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v>[Admin Panel] Broken link</v>
       </c>
-      <c r="E88" s="165"/>
-      <c r="F88" s="165"/>
-      <c r="G88" s="165"/>
-      <c r="H88" s="165"/>
-      <c r="I88" s="165"/>
+      <c r="E88" s="173"/>
+      <c r="F88" s="173"/>
+      <c r="G88" s="173"/>
+      <c r="H88" s="173"/>
+      <c r="I88" s="173"/>
       <c r="J88" s="90"/>
       <c r="K88" s="138" t="str">
         <f>IF(B88="","",IFERROR(VLOOKUP(B88,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -15908,11 +15960,11 @@
         <v>Sprint 5</v>
       </c>
       <c r="T88" s="91"/>
-      <c r="U88" s="167">
+      <c r="U88" s="151">
         <f ca="1">IF(B88="","",IFERROR(VLOOKUP(B88,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v>169</v>
       </c>
-      <c r="V88" s="168"/>
+      <c r="V88" s="152"/>
       <c r="W88" s="73"/>
       <c r="X88" s="88"/>
       <c r="Y88" s="72"/>
@@ -15923,15 +15975,15 @@
         <v>46</v>
       </c>
       <c r="C89" s="107"/>
-      <c r="D89" s="166" t="str">
+      <c r="D89" s="174" t="str">
         <f>IF(B89="","",IFERROR(VLOOKUP(B89,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v>[Payment] Crash on load</v>
       </c>
-      <c r="E89" s="166"/>
-      <c r="F89" s="166"/>
-      <c r="G89" s="166"/>
-      <c r="H89" s="166"/>
-      <c r="I89" s="166"/>
+      <c r="E89" s="174"/>
+      <c r="F89" s="174"/>
+      <c r="G89" s="174"/>
+      <c r="H89" s="174"/>
+      <c r="I89" s="174"/>
       <c r="J89" s="93"/>
       <c r="K89" s="140" t="str">
         <f>IF(B89="","",IFERROR(VLOOKUP(B89,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -15958,11 +16010,11 @@
         <v>Sprint 3</v>
       </c>
       <c r="T89" s="94"/>
-      <c r="U89" s="167">
+      <c r="U89" s="151">
         <f ca="1">IF(B89="","",IFERROR(VLOOKUP(B89,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v>165</v>
       </c>
-      <c r="V89" s="168"/>
+      <c r="V89" s="152"/>
       <c r="W89" s="73"/>
       <c r="X89" s="88"/>
       <c r="Y89" s="72"/>
@@ -15973,15 +16025,15 @@
         <v>48</v>
       </c>
       <c r="C90" s="106"/>
-      <c r="D90" s="165" t="str">
+      <c r="D90" s="173" t="str">
         <f>IF(B90="","",IFERROR(VLOOKUP(B90,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v>[Export] NullPointerException</v>
       </c>
-      <c r="E90" s="165"/>
-      <c r="F90" s="165"/>
-      <c r="G90" s="165"/>
-      <c r="H90" s="165"/>
-      <c r="I90" s="165"/>
+      <c r="E90" s="173"/>
+      <c r="F90" s="173"/>
+      <c r="G90" s="173"/>
+      <c r="H90" s="173"/>
+      <c r="I90" s="173"/>
       <c r="J90" s="90"/>
       <c r="K90" s="138" t="str">
         <f>IF(B90="","",IFERROR(VLOOKUP(B90,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -16008,11 +16060,11 @@
         <v>Sprint 1</v>
       </c>
       <c r="T90" s="91"/>
-      <c r="U90" s="167">
+      <c r="U90" s="151">
         <f ca="1">IF(B90="","",IFERROR(VLOOKUP(B90,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v>159</v>
       </c>
-      <c r="V90" s="168"/>
+      <c r="V90" s="152"/>
       <c r="W90" s="73"/>
       <c r="X90" s="88"/>
       <c r="Y90" s="72"/>
@@ -16023,15 +16075,15 @@
         <v>50</v>
       </c>
       <c r="C91" s="107"/>
-      <c r="D91" s="166" t="str">
+      <c r="D91" s="174" t="str">
         <f>IF(B91="","",IFERROR(VLOOKUP(B91,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v>[Export] Broken link</v>
       </c>
-      <c r="E91" s="166"/>
-      <c r="F91" s="166"/>
-      <c r="G91" s="166"/>
-      <c r="H91" s="166"/>
-      <c r="I91" s="166"/>
+      <c r="E91" s="174"/>
+      <c r="F91" s="174"/>
+      <c r="G91" s="174"/>
+      <c r="H91" s="174"/>
+      <c r="I91" s="174"/>
       <c r="J91" s="93"/>
       <c r="K91" s="140" t="str">
         <f>IF(B91="","",IFERROR(VLOOKUP(B91,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -16058,11 +16110,11 @@
         <v>Sprint 8</v>
       </c>
       <c r="T91" s="94"/>
-      <c r="U91" s="167">
+      <c r="U91" s="151">
         <f ca="1">IF(B91="","",IFERROR(VLOOKUP(B91,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v>149</v>
       </c>
-      <c r="V91" s="168"/>
+      <c r="V91" s="152"/>
       <c r="W91" s="73"/>
       <c r="X91" s="88"/>
       <c r="Y91" s="72"/>
@@ -16073,15 +16125,15 @@
         <v>53</v>
       </c>
       <c r="C92" s="106"/>
-      <c r="D92" s="165" t="str">
+      <c r="D92" s="173" t="str">
         <f>IF(B92="","",IFERROR(VLOOKUP(B92,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v>[Login] NullPointerException</v>
       </c>
-      <c r="E92" s="165"/>
-      <c r="F92" s="165"/>
-      <c r="G92" s="165"/>
-      <c r="H92" s="165"/>
-      <c r="I92" s="165"/>
+      <c r="E92" s="173"/>
+      <c r="F92" s="173"/>
+      <c r="G92" s="173"/>
+      <c r="H92" s="173"/>
+      <c r="I92" s="173"/>
       <c r="J92" s="90"/>
       <c r="K92" s="138" t="str">
         <f>IF(B92="","",IFERROR(VLOOKUP(B92,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -16108,11 +16160,11 @@
         <v>Sprint 1</v>
       </c>
       <c r="T92" s="91"/>
-      <c r="U92" s="167">
+      <c r="U92" s="151">
         <f ca="1">IF(B92="","",IFERROR(VLOOKUP(B92,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v>145</v>
       </c>
-      <c r="V92" s="168"/>
+      <c r="V92" s="152"/>
       <c r="W92" s="73"/>
       <c r="X92" s="88"/>
       <c r="Y92" s="72"/>
@@ -16123,15 +16175,15 @@
         <v>55</v>
       </c>
       <c r="C93" s="107"/>
-      <c r="D93" s="162" t="str">
+      <c r="D93" s="217" t="str">
         <f>IF(B93="","",IFERROR(VLOOKUP(B93,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v>[Dashboard] Memory leak</v>
       </c>
-      <c r="E93" s="162"/>
-      <c r="F93" s="162"/>
-      <c r="G93" s="162"/>
-      <c r="H93" s="162"/>
-      <c r="I93" s="162"/>
+      <c r="E93" s="217"/>
+      <c r="F93" s="217"/>
+      <c r="G93" s="217"/>
+      <c r="H93" s="217"/>
+      <c r="I93" s="217"/>
       <c r="J93" s="93"/>
       <c r="K93" s="140" t="str">
         <f>IF(B93="","",IFERROR(VLOOKUP(B93,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -16158,11 +16210,11 @@
         <v>Sprint 4</v>
       </c>
       <c r="T93" s="94"/>
-      <c r="U93" s="167">
+      <c r="U93" s="151">
         <f ca="1">IF(B93="","",IFERROR(VLOOKUP(B93,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v>144</v>
       </c>
-      <c r="V93" s="168"/>
+      <c r="V93" s="152"/>
       <c r="W93" s="73"/>
       <c r="X93" s="88"/>
       <c r="Y93" s="72"/>
@@ -16171,15 +16223,15 @@
       <c r="A94" s="72"/>
       <c r="B94" s="89"/>
       <c r="C94" s="108"/>
-      <c r="D94" s="152" t="str">
+      <c r="D94" s="241" t="str">
         <f>IF(B94="","",IFERROR(VLOOKUP(B94,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E94" s="153"/>
-      <c r="F94" s="153"/>
-      <c r="G94" s="153"/>
-      <c r="H94" s="153"/>
-      <c r="I94" s="154"/>
+      <c r="E94" s="242"/>
+      <c r="F94" s="242"/>
+      <c r="G94" s="242"/>
+      <c r="H94" s="242"/>
+      <c r="I94" s="243"/>
       <c r="J94" s="103"/>
       <c r="K94" s="138" t="str">
         <f>IF(B94="","",IFERROR(VLOOKUP(B94,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -16206,11 +16258,11 @@
         <v/>
       </c>
       <c r="T94" s="96"/>
-      <c r="U94" s="158" t="str">
+      <c r="U94" s="234" t="str">
         <f>IF(B94="","",IFERROR(VLOOKUP(B94,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V94" s="159"/>
+      <c r="V94" s="235"/>
       <c r="W94" s="73"/>
       <c r="X94" s="88"/>
       <c r="Y94" s="72"/>
@@ -16219,15 +16271,15 @@
       <c r="A95" s="97"/>
       <c r="B95" s="92"/>
       <c r="C95" s="109"/>
-      <c r="D95" s="149" t="str">
+      <c r="D95" s="238" t="str">
         <f>IF(B95="","",IFERROR(VLOOKUP(B95,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E95" s="150"/>
-      <c r="F95" s="150"/>
-      <c r="G95" s="150"/>
-      <c r="H95" s="150"/>
-      <c r="I95" s="151"/>
+      <c r="E95" s="239"/>
+      <c r="F95" s="239"/>
+      <c r="G95" s="239"/>
+      <c r="H95" s="239"/>
+      <c r="I95" s="240"/>
       <c r="J95" s="104"/>
       <c r="K95" s="140" t="str">
         <f>IF(B95="","",IFERROR(VLOOKUP(B95,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -16254,11 +16306,11 @@
         <v/>
       </c>
       <c r="T95" s="99"/>
-      <c r="U95" s="158" t="str">
+      <c r="U95" s="234" t="str">
         <f>IF(B95="","",IFERROR(VLOOKUP(B95,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V95" s="159"/>
+      <c r="V95" s="235"/>
       <c r="W95" s="73"/>
       <c r="X95" s="88"/>
       <c r="Y95" s="97"/>
@@ -16267,15 +16319,15 @@
       <c r="A96" s="97"/>
       <c r="B96" s="89"/>
       <c r="C96" s="108"/>
-      <c r="D96" s="152" t="str">
+      <c r="D96" s="241" t="str">
         <f>IF(B96="","",IFERROR(VLOOKUP(B96,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E96" s="153"/>
-      <c r="F96" s="153"/>
-      <c r="G96" s="153"/>
-      <c r="H96" s="153"/>
-      <c r="I96" s="154"/>
+      <c r="E96" s="242"/>
+      <c r="F96" s="242"/>
+      <c r="G96" s="242"/>
+      <c r="H96" s="242"/>
+      <c r="I96" s="243"/>
       <c r="J96" s="103"/>
       <c r="K96" s="138" t="str">
         <f>IF(B96="","",IFERROR(VLOOKUP(B96,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -16302,11 +16354,11 @@
         <v/>
       </c>
       <c r="T96" s="96"/>
-      <c r="U96" s="158" t="str">
+      <c r="U96" s="234" t="str">
         <f>IF(B96="","",IFERROR(VLOOKUP(B96,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V96" s="159"/>
+      <c r="V96" s="235"/>
       <c r="W96" s="73"/>
       <c r="X96" s="88"/>
       <c r="Y96" s="97"/>
@@ -16315,15 +16367,15 @@
       <c r="A97" s="97"/>
       <c r="B97" s="92"/>
       <c r="C97" s="109"/>
-      <c r="D97" s="149" t="str">
+      <c r="D97" s="238" t="str">
         <f>IF(B97="","",IFERROR(VLOOKUP(B97,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E97" s="150"/>
-      <c r="F97" s="150"/>
-      <c r="G97" s="150"/>
-      <c r="H97" s="150"/>
-      <c r="I97" s="151"/>
+      <c r="E97" s="239"/>
+      <c r="F97" s="239"/>
+      <c r="G97" s="239"/>
+      <c r="H97" s="239"/>
+      <c r="I97" s="240"/>
       <c r="J97" s="104"/>
       <c r="K97" s="140" t="str">
         <f>IF(B97="","",IFERROR(VLOOKUP(B97,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -16350,11 +16402,11 @@
         <v/>
       </c>
       <c r="T97" s="99"/>
-      <c r="U97" s="158" t="str">
+      <c r="U97" s="234" t="str">
         <f>IF(B97="","",IFERROR(VLOOKUP(B97,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V97" s="159"/>
+      <c r="V97" s="235"/>
       <c r="W97" s="73"/>
       <c r="X97" s="88"/>
       <c r="Y97" s="97"/>
@@ -16363,15 +16415,15 @@
       <c r="A98" s="97"/>
       <c r="B98" s="89"/>
       <c r="C98" s="108"/>
-      <c r="D98" s="152" t="str">
+      <c r="D98" s="241" t="str">
         <f>IF(B98="","",IFERROR(VLOOKUP(B98,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E98" s="153"/>
-      <c r="F98" s="153"/>
-      <c r="G98" s="153"/>
-      <c r="H98" s="153"/>
-      <c r="I98" s="154"/>
+      <c r="E98" s="242"/>
+      <c r="F98" s="242"/>
+      <c r="G98" s="242"/>
+      <c r="H98" s="242"/>
+      <c r="I98" s="243"/>
       <c r="J98" s="103"/>
       <c r="K98" s="138" t="str">
         <f>IF(B98="","",IFERROR(VLOOKUP(B98,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -16398,11 +16450,11 @@
         <v/>
       </c>
       <c r="T98" s="96"/>
-      <c r="U98" s="158" t="str">
+      <c r="U98" s="234" t="str">
         <f>IF(B98="","",IFERROR(VLOOKUP(B98,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V98" s="159"/>
+      <c r="V98" s="235"/>
       <c r="W98" s="73"/>
       <c r="X98" s="88"/>
       <c r="Y98" s="97"/>
@@ -16411,15 +16463,15 @@
       <c r="A99" s="97"/>
       <c r="B99" s="92"/>
       <c r="C99" s="109"/>
-      <c r="D99" s="149" t="str">
+      <c r="D99" s="238" t="str">
         <f>IF(B99="","",IFERROR(VLOOKUP(B99,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E99" s="150"/>
-      <c r="F99" s="150"/>
-      <c r="G99" s="150"/>
-      <c r="H99" s="150"/>
-      <c r="I99" s="151"/>
+      <c r="E99" s="239"/>
+      <c r="F99" s="239"/>
+      <c r="G99" s="239"/>
+      <c r="H99" s="239"/>
+      <c r="I99" s="240"/>
       <c r="J99" s="104"/>
       <c r="K99" s="140" t="str">
         <f>IF(B99="","",IFERROR(VLOOKUP(B99,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -16446,11 +16498,11 @@
         <v/>
       </c>
       <c r="T99" s="99"/>
-      <c r="U99" s="158" t="str">
+      <c r="U99" s="234" t="str">
         <f>IF(B99="","",IFERROR(VLOOKUP(B99,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V99" s="159"/>
+      <c r="V99" s="235"/>
       <c r="W99" s="73"/>
       <c r="X99" s="88"/>
       <c r="Y99" s="97"/>
@@ -16459,15 +16511,15 @@
       <c r="A100" s="97"/>
       <c r="B100" s="89"/>
       <c r="C100" s="108"/>
-      <c r="D100" s="152" t="str">
+      <c r="D100" s="241" t="str">
         <f>IF(B100="","",IFERROR(VLOOKUP(B100,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E100" s="153"/>
-      <c r="F100" s="153"/>
-      <c r="G100" s="153"/>
-      <c r="H100" s="153"/>
-      <c r="I100" s="154"/>
+      <c r="E100" s="242"/>
+      <c r="F100" s="242"/>
+      <c r="G100" s="242"/>
+      <c r="H100" s="242"/>
+      <c r="I100" s="243"/>
       <c r="J100" s="103"/>
       <c r="K100" s="138" t="str">
         <f>IF(B100="","",IFERROR(VLOOKUP(B100,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -16494,11 +16546,11 @@
         <v/>
       </c>
       <c r="T100" s="96"/>
-      <c r="U100" s="158" t="str">
+      <c r="U100" s="234" t="str">
         <f>IF(B100="","",IFERROR(VLOOKUP(B100,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V100" s="159"/>
+      <c r="V100" s="235"/>
       <c r="W100" s="73"/>
       <c r="X100" s="88"/>
       <c r="Y100" s="97"/>
@@ -16507,15 +16559,15 @@
       <c r="A101" s="97"/>
       <c r="B101" s="92"/>
       <c r="C101" s="109"/>
-      <c r="D101" s="149" t="str">
+      <c r="D101" s="238" t="str">
         <f>IF(B101="","",IFERROR(VLOOKUP(B101,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E101" s="150"/>
-      <c r="F101" s="150"/>
-      <c r="G101" s="150"/>
-      <c r="H101" s="150"/>
-      <c r="I101" s="151"/>
+      <c r="E101" s="239"/>
+      <c r="F101" s="239"/>
+      <c r="G101" s="239"/>
+      <c r="H101" s="239"/>
+      <c r="I101" s="240"/>
       <c r="J101" s="104"/>
       <c r="K101" s="140" t="str">
         <f>IF(B101="","",IFERROR(VLOOKUP(B101,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -16542,11 +16594,11 @@
         <v/>
       </c>
       <c r="T101" s="99"/>
-      <c r="U101" s="158" t="str">
+      <c r="U101" s="234" t="str">
         <f>IF(B101="","",IFERROR(VLOOKUP(B101,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V101" s="159"/>
+      <c r="V101" s="235"/>
       <c r="W101" s="73"/>
       <c r="X101" s="88"/>
       <c r="Y101" s="97"/>
@@ -16555,15 +16607,15 @@
       <c r="A102" s="97"/>
       <c r="B102" s="89"/>
       <c r="C102" s="108"/>
-      <c r="D102" s="152" t="str">
+      <c r="D102" s="241" t="str">
         <f>IF(B102="","",IFERROR(VLOOKUP(B102,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E102" s="153"/>
-      <c r="F102" s="153"/>
-      <c r="G102" s="153"/>
-      <c r="H102" s="153"/>
-      <c r="I102" s="154"/>
+      <c r="E102" s="242"/>
+      <c r="F102" s="242"/>
+      <c r="G102" s="242"/>
+      <c r="H102" s="242"/>
+      <c r="I102" s="243"/>
       <c r="J102" s="103"/>
       <c r="K102" s="138" t="str">
         <f>IF(B102="","",IFERROR(VLOOKUP(B102,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -16590,11 +16642,11 @@
         <v/>
       </c>
       <c r="T102" s="96"/>
-      <c r="U102" s="158" t="str">
+      <c r="U102" s="234" t="str">
         <f>IF(B102="","",IFERROR(VLOOKUP(B102,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V102" s="159"/>
+      <c r="V102" s="235"/>
       <c r="W102" s="73"/>
       <c r="X102" s="88"/>
       <c r="Y102" s="97"/>
@@ -16603,15 +16655,15 @@
       <c r="A103" s="97"/>
       <c r="B103" s="92"/>
       <c r="C103" s="109"/>
-      <c r="D103" s="149" t="str">
+      <c r="D103" s="238" t="str">
         <f>IF(B103="","",IFERROR(VLOOKUP(B103,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E103" s="150"/>
-      <c r="F103" s="150"/>
-      <c r="G103" s="150"/>
-      <c r="H103" s="150"/>
-      <c r="I103" s="151"/>
+      <c r="E103" s="239"/>
+      <c r="F103" s="239"/>
+      <c r="G103" s="239"/>
+      <c r="H103" s="239"/>
+      <c r="I103" s="240"/>
       <c r="J103" s="104"/>
       <c r="K103" s="140" t="str">
         <f>IF(B103="","",IFERROR(VLOOKUP(B103,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -16638,11 +16690,11 @@
         <v/>
       </c>
       <c r="T103" s="99"/>
-      <c r="U103" s="158" t="str">
+      <c r="U103" s="234" t="str">
         <f>IF(B103="","",IFERROR(VLOOKUP(B103,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V103" s="159"/>
+      <c r="V103" s="235"/>
       <c r="W103" s="73"/>
       <c r="X103" s="88"/>
       <c r="Y103" s="97"/>
@@ -16651,15 +16703,15 @@
       <c r="A104" s="97"/>
       <c r="B104" s="89"/>
       <c r="C104" s="108"/>
-      <c r="D104" s="152" t="str">
+      <c r="D104" s="241" t="str">
         <f>IF(B104="","",IFERROR(VLOOKUP(B104,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E104" s="153"/>
-      <c r="F104" s="153"/>
-      <c r="G104" s="153"/>
-      <c r="H104" s="153"/>
-      <c r="I104" s="154"/>
+      <c r="E104" s="242"/>
+      <c r="F104" s="242"/>
+      <c r="G104" s="242"/>
+      <c r="H104" s="242"/>
+      <c r="I104" s="243"/>
       <c r="J104" s="103"/>
       <c r="K104" s="138" t="str">
         <f>IF(B104="","",IFERROR(VLOOKUP(B104,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -16686,11 +16738,11 @@
         <v/>
       </c>
       <c r="T104" s="96"/>
-      <c r="U104" s="158" t="str">
+      <c r="U104" s="234" t="str">
         <f>IF(B104="","",IFERROR(VLOOKUP(B104,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V104" s="159"/>
+      <c r="V104" s="235"/>
       <c r="W104" s="73"/>
       <c r="X104" s="88"/>
       <c r="Y104" s="97"/>
@@ -16699,15 +16751,15 @@
       <c r="A105" s="97"/>
       <c r="B105" s="92"/>
       <c r="C105" s="109"/>
-      <c r="D105" s="149" t="str">
+      <c r="D105" s="238" t="str">
         <f>IF(B105="","",IFERROR(VLOOKUP(B105,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E105" s="150"/>
-      <c r="F105" s="150"/>
-      <c r="G105" s="150"/>
-      <c r="H105" s="150"/>
-      <c r="I105" s="151"/>
+      <c r="E105" s="239"/>
+      <c r="F105" s="239"/>
+      <c r="G105" s="239"/>
+      <c r="H105" s="239"/>
+      <c r="I105" s="240"/>
       <c r="J105" s="104"/>
       <c r="K105" s="140" t="str">
         <f>IF(B105="","",IFERROR(VLOOKUP(B105,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -16734,11 +16786,11 @@
         <v/>
       </c>
       <c r="T105" s="99"/>
-      <c r="U105" s="158" t="str">
+      <c r="U105" s="234" t="str">
         <f>IF(B105="","",IFERROR(VLOOKUP(B105,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V105" s="159"/>
+      <c r="V105" s="235"/>
       <c r="W105" s="73"/>
       <c r="X105" s="88"/>
       <c r="Y105" s="97"/>
@@ -16747,15 +16799,15 @@
       <c r="A106" s="97"/>
       <c r="B106" s="89"/>
       <c r="C106" s="108"/>
-      <c r="D106" s="152" t="str">
+      <c r="D106" s="241" t="str">
         <f>IF(B106="","",IFERROR(VLOOKUP(B106,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E106" s="153"/>
-      <c r="F106" s="153"/>
-      <c r="G106" s="153"/>
-      <c r="H106" s="153"/>
-      <c r="I106" s="154"/>
+      <c r="E106" s="242"/>
+      <c r="F106" s="242"/>
+      <c r="G106" s="242"/>
+      <c r="H106" s="242"/>
+      <c r="I106" s="243"/>
       <c r="J106" s="103"/>
       <c r="K106" s="138" t="str">
         <f>IF(B106="","",IFERROR(VLOOKUP(B106,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -16782,11 +16834,11 @@
         <v/>
       </c>
       <c r="T106" s="96"/>
-      <c r="U106" s="158" t="str">
+      <c r="U106" s="234" t="str">
         <f>IF(B106="","",IFERROR(VLOOKUP(B106,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V106" s="159"/>
+      <c r="V106" s="235"/>
       <c r="W106" s="73"/>
       <c r="X106" s="88"/>
       <c r="Y106" s="97"/>
@@ -16795,15 +16847,15 @@
       <c r="A107" s="97"/>
       <c r="B107" s="92"/>
       <c r="C107" s="109"/>
-      <c r="D107" s="149" t="str">
+      <c r="D107" s="238" t="str">
         <f>IF(B107="","",IFERROR(VLOOKUP(B107,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E107" s="150"/>
-      <c r="F107" s="150"/>
-      <c r="G107" s="150"/>
-      <c r="H107" s="150"/>
-      <c r="I107" s="151"/>
+      <c r="E107" s="239"/>
+      <c r="F107" s="239"/>
+      <c r="G107" s="239"/>
+      <c r="H107" s="239"/>
+      <c r="I107" s="240"/>
       <c r="J107" s="104"/>
       <c r="K107" s="140" t="str">
         <f>IF(B107="","",IFERROR(VLOOKUP(B107,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -16830,11 +16882,11 @@
         <v/>
       </c>
       <c r="T107" s="99"/>
-      <c r="U107" s="158" t="str">
+      <c r="U107" s="234" t="str">
         <f>IF(B107="","",IFERROR(VLOOKUP(B107,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V107" s="159"/>
+      <c r="V107" s="235"/>
       <c r="W107" s="73"/>
       <c r="X107" s="88"/>
       <c r="Y107" s="97"/>
@@ -16843,15 +16895,15 @@
       <c r="A108" s="97"/>
       <c r="B108" s="89"/>
       <c r="C108" s="108"/>
-      <c r="D108" s="152" t="str">
+      <c r="D108" s="241" t="str">
         <f>IF(B108="","",IFERROR(VLOOKUP(B108,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E108" s="153"/>
-      <c r="F108" s="153"/>
-      <c r="G108" s="153"/>
-      <c r="H108" s="153"/>
-      <c r="I108" s="154"/>
+      <c r="E108" s="242"/>
+      <c r="F108" s="242"/>
+      <c r="G108" s="242"/>
+      <c r="H108" s="242"/>
+      <c r="I108" s="243"/>
       <c r="J108" s="103"/>
       <c r="K108" s="138" t="str">
         <f>IF(B108="","",IFERROR(VLOOKUP(B108,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -16878,11 +16930,11 @@
         <v/>
       </c>
       <c r="T108" s="96"/>
-      <c r="U108" s="158" t="str">
+      <c r="U108" s="234" t="str">
         <f>IF(B108="","",IFERROR(VLOOKUP(B108,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V108" s="159"/>
+      <c r="V108" s="235"/>
       <c r="W108" s="73"/>
       <c r="X108" s="88"/>
       <c r="Y108" s="97"/>
@@ -16891,15 +16943,15 @@
       <c r="A109" s="97"/>
       <c r="B109" s="92"/>
       <c r="C109" s="109"/>
-      <c r="D109" s="149" t="str">
+      <c r="D109" s="238" t="str">
         <f>IF(B109="","",IFERROR(VLOOKUP(B109,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E109" s="150"/>
-      <c r="F109" s="150"/>
-      <c r="G109" s="150"/>
-      <c r="H109" s="150"/>
-      <c r="I109" s="151"/>
+      <c r="E109" s="239"/>
+      <c r="F109" s="239"/>
+      <c r="G109" s="239"/>
+      <c r="H109" s="239"/>
+      <c r="I109" s="240"/>
       <c r="J109" s="104"/>
       <c r="K109" s="140" t="str">
         <f>IF(B109="","",IFERROR(VLOOKUP(B109,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -16926,11 +16978,11 @@
         <v/>
       </c>
       <c r="T109" s="99"/>
-      <c r="U109" s="158" t="str">
+      <c r="U109" s="234" t="str">
         <f>IF(B109="","",IFERROR(VLOOKUP(B109,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V109" s="159"/>
+      <c r="V109" s="235"/>
       <c r="W109" s="73"/>
       <c r="X109" s="88"/>
       <c r="Y109" s="97"/>
@@ -16939,15 +16991,15 @@
       <c r="A110" s="97"/>
       <c r="B110" s="89"/>
       <c r="C110" s="108"/>
-      <c r="D110" s="152" t="str">
+      <c r="D110" s="241" t="str">
         <f>IF(B110="","",IFERROR(VLOOKUP(B110,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E110" s="153"/>
-      <c r="F110" s="153"/>
-      <c r="G110" s="153"/>
-      <c r="H110" s="153"/>
-      <c r="I110" s="154"/>
+      <c r="E110" s="242"/>
+      <c r="F110" s="242"/>
+      <c r="G110" s="242"/>
+      <c r="H110" s="242"/>
+      <c r="I110" s="243"/>
       <c r="J110" s="103"/>
       <c r="K110" s="138" t="str">
         <f>IF(B110="","",IFERROR(VLOOKUP(B110,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -16974,11 +17026,11 @@
         <v/>
       </c>
       <c r="T110" s="96"/>
-      <c r="U110" s="158" t="str">
+      <c r="U110" s="234" t="str">
         <f>IF(B110="","",IFERROR(VLOOKUP(B110,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V110" s="159"/>
+      <c r="V110" s="235"/>
       <c r="W110" s="73"/>
       <c r="X110" s="88"/>
       <c r="Y110" s="97"/>
@@ -16987,15 +17039,15 @@
       <c r="A111" s="97"/>
       <c r="B111" s="92"/>
       <c r="C111" s="109"/>
-      <c r="D111" s="149" t="str">
+      <c r="D111" s="238" t="str">
         <f>IF(B111="","",IFERROR(VLOOKUP(B111,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E111" s="150"/>
-      <c r="F111" s="150"/>
-      <c r="G111" s="150"/>
-      <c r="H111" s="150"/>
-      <c r="I111" s="151"/>
+      <c r="E111" s="239"/>
+      <c r="F111" s="239"/>
+      <c r="G111" s="239"/>
+      <c r="H111" s="239"/>
+      <c r="I111" s="240"/>
       <c r="J111" s="104"/>
       <c r="K111" s="140" t="str">
         <f>IF(B111="","",IFERROR(VLOOKUP(B111,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -17022,11 +17074,11 @@
         <v/>
       </c>
       <c r="T111" s="99"/>
-      <c r="U111" s="158" t="str">
+      <c r="U111" s="234" t="str">
         <f>IF(B111="","",IFERROR(VLOOKUP(B111,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V111" s="159"/>
+      <c r="V111" s="235"/>
       <c r="W111" s="73"/>
       <c r="X111" s="88"/>
       <c r="Y111" s="97"/>
@@ -17035,15 +17087,15 @@
       <c r="A112" s="97"/>
       <c r="B112" s="89"/>
       <c r="C112" s="108"/>
-      <c r="D112" s="152" t="str">
+      <c r="D112" s="241" t="str">
         <f>IF(B112="","",IFERROR(VLOOKUP(B112,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E112" s="153"/>
-      <c r="F112" s="153"/>
-      <c r="G112" s="153"/>
-      <c r="H112" s="153"/>
-      <c r="I112" s="154"/>
+      <c r="E112" s="242"/>
+      <c r="F112" s="242"/>
+      <c r="G112" s="242"/>
+      <c r="H112" s="242"/>
+      <c r="I112" s="243"/>
       <c r="J112" s="103"/>
       <c r="K112" s="138" t="str">
         <f>IF(B112="","",IFERROR(VLOOKUP(B112,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -17070,11 +17122,11 @@
         <v/>
       </c>
       <c r="T112" s="96"/>
-      <c r="U112" s="158" t="str">
+      <c r="U112" s="234" t="str">
         <f>IF(B112="","",IFERROR(VLOOKUP(B112,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V112" s="159"/>
+      <c r="V112" s="235"/>
       <c r="W112" s="73"/>
       <c r="X112" s="88"/>
       <c r="Y112" s="97"/>
@@ -17083,15 +17135,15 @@
       <c r="A113" s="97"/>
       <c r="B113" s="92"/>
       <c r="C113" s="109"/>
-      <c r="D113" s="149" t="str">
+      <c r="D113" s="238" t="str">
         <f>IF(B113="","",IFERROR(VLOOKUP(B113,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E113" s="150"/>
-      <c r="F113" s="150"/>
-      <c r="G113" s="150"/>
-      <c r="H113" s="150"/>
-      <c r="I113" s="151"/>
+      <c r="E113" s="239"/>
+      <c r="F113" s="239"/>
+      <c r="G113" s="239"/>
+      <c r="H113" s="239"/>
+      <c r="I113" s="240"/>
       <c r="J113" s="104"/>
       <c r="K113" s="140" t="str">
         <f>IF(B113="","",IFERROR(VLOOKUP(B113,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -17118,11 +17170,11 @@
         <v/>
       </c>
       <c r="T113" s="99"/>
-      <c r="U113" s="158" t="str">
+      <c r="U113" s="234" t="str">
         <f>IF(B113="","",IFERROR(VLOOKUP(B113,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V113" s="159"/>
+      <c r="V113" s="235"/>
       <c r="W113" s="73"/>
       <c r="X113" s="88"/>
       <c r="Y113" s="97"/>
@@ -17131,15 +17183,15 @@
       <c r="A114" s="97"/>
       <c r="B114" s="89"/>
       <c r="C114" s="108"/>
-      <c r="D114" s="152" t="str">
+      <c r="D114" s="241" t="str">
         <f>IF(B114="","",IFERROR(VLOOKUP(B114,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E114" s="153"/>
-      <c r="F114" s="153"/>
-      <c r="G114" s="153"/>
-      <c r="H114" s="153"/>
-      <c r="I114" s="154"/>
+      <c r="E114" s="242"/>
+      <c r="F114" s="242"/>
+      <c r="G114" s="242"/>
+      <c r="H114" s="242"/>
+      <c r="I114" s="243"/>
       <c r="J114" s="103"/>
       <c r="K114" s="138" t="str">
         <f>IF(B114="","",IFERROR(VLOOKUP(B114,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -17166,11 +17218,11 @@
         <v/>
       </c>
       <c r="T114" s="96"/>
-      <c r="U114" s="158" t="str">
+      <c r="U114" s="234" t="str">
         <f>IF(B114="","",IFERROR(VLOOKUP(B114,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V114" s="159"/>
+      <c r="V114" s="235"/>
       <c r="W114" s="73"/>
       <c r="X114" s="88"/>
       <c r="Y114" s="97"/>
@@ -17179,15 +17231,15 @@
       <c r="A115" s="97"/>
       <c r="B115" s="92"/>
       <c r="C115" s="109"/>
-      <c r="D115" s="149" t="str">
+      <c r="D115" s="238" t="str">
         <f>IF(B115="","",IFERROR(VLOOKUP(B115,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E115" s="150"/>
-      <c r="F115" s="150"/>
-      <c r="G115" s="150"/>
-      <c r="H115" s="150"/>
-      <c r="I115" s="151"/>
+      <c r="E115" s="239"/>
+      <c r="F115" s="239"/>
+      <c r="G115" s="239"/>
+      <c r="H115" s="239"/>
+      <c r="I115" s="240"/>
       <c r="J115" s="104"/>
       <c r="K115" s="140" t="str">
         <f>IF(B115="","",IFERROR(VLOOKUP(B115,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -17214,11 +17266,11 @@
         <v/>
       </c>
       <c r="T115" s="99"/>
-      <c r="U115" s="158" t="str">
+      <c r="U115" s="234" t="str">
         <f>IF(B115="","",IFERROR(VLOOKUP(B115,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V115" s="159"/>
+      <c r="V115" s="235"/>
       <c r="W115" s="73"/>
       <c r="X115" s="88"/>
       <c r="Y115" s="97"/>
@@ -17227,15 +17279,15 @@
       <c r="A116" s="97"/>
       <c r="B116" s="89"/>
       <c r="C116" s="108"/>
-      <c r="D116" s="152" t="str">
+      <c r="D116" s="241" t="str">
         <f>IF(B116="","",IFERROR(VLOOKUP(B116,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E116" s="153"/>
-      <c r="F116" s="153"/>
-      <c r="G116" s="153"/>
-      <c r="H116" s="153"/>
-      <c r="I116" s="154"/>
+      <c r="E116" s="242"/>
+      <c r="F116" s="242"/>
+      <c r="G116" s="242"/>
+      <c r="H116" s="242"/>
+      <c r="I116" s="243"/>
       <c r="J116" s="103"/>
       <c r="K116" s="138" t="str">
         <f>IF(B116="","",IFERROR(VLOOKUP(B116,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -17262,11 +17314,11 @@
         <v/>
       </c>
       <c r="T116" s="96"/>
-      <c r="U116" s="158" t="str">
+      <c r="U116" s="234" t="str">
         <f>IF(B116="","",IFERROR(VLOOKUP(B116,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V116" s="159"/>
+      <c r="V116" s="235"/>
       <c r="W116" s="73"/>
       <c r="X116" s="88"/>
       <c r="Y116" s="97"/>
@@ -17275,15 +17327,15 @@
       <c r="A117" s="97"/>
       <c r="B117" s="92"/>
       <c r="C117" s="109"/>
-      <c r="D117" s="149" t="str">
+      <c r="D117" s="238" t="str">
         <f>IF(B117="","",IFERROR(VLOOKUP(B117,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E117" s="150"/>
-      <c r="F117" s="150"/>
-      <c r="G117" s="150"/>
-      <c r="H117" s="150"/>
-      <c r="I117" s="151"/>
+      <c r="E117" s="239"/>
+      <c r="F117" s="239"/>
+      <c r="G117" s="239"/>
+      <c r="H117" s="239"/>
+      <c r="I117" s="240"/>
       <c r="J117" s="104"/>
       <c r="K117" s="140" t="str">
         <f>IF(B117="","",IFERROR(VLOOKUP(B117,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -17310,11 +17362,11 @@
         <v/>
       </c>
       <c r="T117" s="99"/>
-      <c r="U117" s="158" t="str">
+      <c r="U117" s="234" t="str">
         <f>IF(B117="","",IFERROR(VLOOKUP(B117,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V117" s="159"/>
+      <c r="V117" s="235"/>
       <c r="W117" s="73"/>
       <c r="X117" s="88"/>
       <c r="Y117" s="97"/>
@@ -17323,15 +17375,15 @@
       <c r="A118" s="97"/>
       <c r="B118" s="89"/>
       <c r="C118" s="108"/>
-      <c r="D118" s="152" t="str">
+      <c r="D118" s="241" t="str">
         <f>IF(B118="","",IFERROR(VLOOKUP(B118,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E118" s="153"/>
-      <c r="F118" s="153"/>
-      <c r="G118" s="153"/>
-      <c r="H118" s="153"/>
-      <c r="I118" s="154"/>
+      <c r="E118" s="242"/>
+      <c r="F118" s="242"/>
+      <c r="G118" s="242"/>
+      <c r="H118" s="242"/>
+      <c r="I118" s="243"/>
       <c r="J118" s="103"/>
       <c r="K118" s="138" t="str">
         <f>IF(B118="","",IFERROR(VLOOKUP(B118,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -17358,11 +17410,11 @@
         <v/>
       </c>
       <c r="T118" s="96"/>
-      <c r="U118" s="158" t="str">
+      <c r="U118" s="234" t="str">
         <f>IF(B118="","",IFERROR(VLOOKUP(B118,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V118" s="159"/>
+      <c r="V118" s="235"/>
       <c r="W118" s="73"/>
       <c r="X118" s="88"/>
       <c r="Y118" s="97"/>
@@ -17371,15 +17423,15 @@
       <c r="A119" s="97"/>
       <c r="B119" s="92"/>
       <c r="C119" s="109"/>
-      <c r="D119" s="149" t="str">
+      <c r="D119" s="238" t="str">
         <f>IF(B119="","",IFERROR(VLOOKUP(B119,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E119" s="150"/>
-      <c r="F119" s="150"/>
-      <c r="G119" s="150"/>
-      <c r="H119" s="150"/>
-      <c r="I119" s="151"/>
+      <c r="E119" s="239"/>
+      <c r="F119" s="239"/>
+      <c r="G119" s="239"/>
+      <c r="H119" s="239"/>
+      <c r="I119" s="240"/>
       <c r="J119" s="104"/>
       <c r="K119" s="140" t="str">
         <f>IF(B119="","",IFERROR(VLOOKUP(B119,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -17406,11 +17458,11 @@
         <v/>
       </c>
       <c r="T119" s="99"/>
-      <c r="U119" s="158" t="str">
+      <c r="U119" s="234" t="str">
         <f>IF(B119="","",IFERROR(VLOOKUP(B119,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V119" s="159"/>
+      <c r="V119" s="235"/>
       <c r="W119" s="73"/>
       <c r="X119" s="88"/>
       <c r="Y119" s="97"/>
@@ -17419,15 +17471,15 @@
       <c r="A120" s="97"/>
       <c r="B120" s="89"/>
       <c r="C120" s="108"/>
-      <c r="D120" s="152" t="str">
+      <c r="D120" s="241" t="str">
         <f>IF(B120="","",IFERROR(VLOOKUP(B120,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E120" s="153"/>
-      <c r="F120" s="153"/>
-      <c r="G120" s="153"/>
-      <c r="H120" s="153"/>
-      <c r="I120" s="154"/>
+      <c r="E120" s="242"/>
+      <c r="F120" s="242"/>
+      <c r="G120" s="242"/>
+      <c r="H120" s="242"/>
+      <c r="I120" s="243"/>
       <c r="J120" s="103"/>
       <c r="K120" s="138" t="str">
         <f>IF(B120="","",IFERROR(VLOOKUP(B120,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -17454,11 +17506,11 @@
         <v/>
       </c>
       <c r="T120" s="96"/>
-      <c r="U120" s="158" t="str">
+      <c r="U120" s="234" t="str">
         <f>IF(B120="","",IFERROR(VLOOKUP(B120,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V120" s="159"/>
+      <c r="V120" s="235"/>
       <c r="W120" s="73"/>
       <c r="X120" s="88"/>
       <c r="Y120" s="97"/>
@@ -17467,15 +17519,15 @@
       <c r="A121" s="97"/>
       <c r="B121" s="92"/>
       <c r="C121" s="109"/>
-      <c r="D121" s="149" t="str">
+      <c r="D121" s="238" t="str">
         <f>IF(B121="","",IFERROR(VLOOKUP(B121,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E121" s="150"/>
-      <c r="F121" s="150"/>
-      <c r="G121" s="150"/>
-      <c r="H121" s="150"/>
-      <c r="I121" s="151"/>
+      <c r="E121" s="239"/>
+      <c r="F121" s="239"/>
+      <c r="G121" s="239"/>
+      <c r="H121" s="239"/>
+      <c r="I121" s="240"/>
       <c r="J121" s="104"/>
       <c r="K121" s="140" t="str">
         <f>IF(B121="","",IFERROR(VLOOKUP(B121,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -17502,11 +17554,11 @@
         <v/>
       </c>
       <c r="T121" s="99"/>
-      <c r="U121" s="158" t="str">
+      <c r="U121" s="234" t="str">
         <f>IF(B121="","",IFERROR(VLOOKUP(B121,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V121" s="159"/>
+      <c r="V121" s="235"/>
       <c r="W121" s="73"/>
       <c r="X121" s="88"/>
       <c r="Y121" s="97"/>
@@ -17515,15 +17567,15 @@
       <c r="A122" s="97"/>
       <c r="B122" s="89"/>
       <c r="C122" s="108"/>
-      <c r="D122" s="152" t="str">
+      <c r="D122" s="241" t="str">
         <f>IF(B122="","",IFERROR(VLOOKUP(B122,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E122" s="153"/>
-      <c r="F122" s="153"/>
-      <c r="G122" s="153"/>
-      <c r="H122" s="153"/>
-      <c r="I122" s="154"/>
+      <c r="E122" s="242"/>
+      <c r="F122" s="242"/>
+      <c r="G122" s="242"/>
+      <c r="H122" s="242"/>
+      <c r="I122" s="243"/>
       <c r="J122" s="103"/>
       <c r="K122" s="138" t="str">
         <f>IF(B122="","",IFERROR(VLOOKUP(B122,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -17550,11 +17602,11 @@
         <v/>
       </c>
       <c r="T122" s="96"/>
-      <c r="U122" s="158" t="str">
+      <c r="U122" s="234" t="str">
         <f>IF(B122="","",IFERROR(VLOOKUP(B122,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V122" s="159"/>
+      <c r="V122" s="235"/>
       <c r="W122" s="73"/>
       <c r="X122" s="88"/>
       <c r="Y122" s="97"/>
@@ -17563,15 +17615,15 @@
       <c r="A123" s="97"/>
       <c r="B123" s="92"/>
       <c r="C123" s="109"/>
-      <c r="D123" s="149" t="str">
+      <c r="D123" s="238" t="str">
         <f>IF(B123="","",IFERROR(VLOOKUP(B123,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E123" s="150"/>
-      <c r="F123" s="150"/>
-      <c r="G123" s="150"/>
-      <c r="H123" s="150"/>
-      <c r="I123" s="151"/>
+      <c r="E123" s="239"/>
+      <c r="F123" s="239"/>
+      <c r="G123" s="239"/>
+      <c r="H123" s="239"/>
+      <c r="I123" s="240"/>
       <c r="J123" s="104"/>
       <c r="K123" s="140" t="str">
         <f>IF(B123="","",IFERROR(VLOOKUP(B123,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -17598,11 +17650,11 @@
         <v/>
       </c>
       <c r="T123" s="99"/>
-      <c r="U123" s="158" t="str">
+      <c r="U123" s="234" t="str">
         <f>IF(B123="","",IFERROR(VLOOKUP(B123,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V123" s="159"/>
+      <c r="V123" s="235"/>
       <c r="W123" s="73"/>
       <c r="X123" s="88"/>
       <c r="Y123" s="97"/>
@@ -17611,15 +17663,15 @@
       <c r="A124" s="97"/>
       <c r="B124" s="89"/>
       <c r="C124" s="108"/>
-      <c r="D124" s="152" t="str">
+      <c r="D124" s="241" t="str">
         <f>IF(B124="","",IFERROR(VLOOKUP(B124,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E124" s="153"/>
-      <c r="F124" s="153"/>
-      <c r="G124" s="153"/>
-      <c r="H124" s="153"/>
-      <c r="I124" s="154"/>
+      <c r="E124" s="242"/>
+      <c r="F124" s="242"/>
+      <c r="G124" s="242"/>
+      <c r="H124" s="242"/>
+      <c r="I124" s="243"/>
       <c r="J124" s="103"/>
       <c r="K124" s="138" t="str">
         <f>IF(B124="","",IFERROR(VLOOKUP(B124,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -17646,11 +17698,11 @@
         <v/>
       </c>
       <c r="T124" s="96"/>
-      <c r="U124" s="158" t="str">
+      <c r="U124" s="234" t="str">
         <f>IF(B124="","",IFERROR(VLOOKUP(B124,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V124" s="159"/>
+      <c r="V124" s="235"/>
       <c r="W124" s="73"/>
       <c r="X124" s="88"/>
       <c r="Y124" s="97"/>
@@ -17659,15 +17711,15 @@
       <c r="A125" s="97"/>
       <c r="B125" s="92"/>
       <c r="C125" s="109"/>
-      <c r="D125" s="149" t="str">
+      <c r="D125" s="238" t="str">
         <f>IF(B125="","",IFERROR(VLOOKUP(B125,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E125" s="150"/>
-      <c r="F125" s="150"/>
-      <c r="G125" s="150"/>
-      <c r="H125" s="150"/>
-      <c r="I125" s="151"/>
+      <c r="E125" s="239"/>
+      <c r="F125" s="239"/>
+      <c r="G125" s="239"/>
+      <c r="H125" s="239"/>
+      <c r="I125" s="240"/>
       <c r="J125" s="104"/>
       <c r="K125" s="140" t="str">
         <f>IF(B125="","",IFERROR(VLOOKUP(B125,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -17694,11 +17746,11 @@
         <v/>
       </c>
       <c r="T125" s="99"/>
-      <c r="U125" s="158" t="str">
+      <c r="U125" s="234" t="str">
         <f>IF(B125="","",IFERROR(VLOOKUP(B125,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V125" s="159"/>
+      <c r="V125" s="235"/>
       <c r="W125" s="73"/>
       <c r="X125" s="88"/>
       <c r="Y125" s="97"/>
@@ -17707,15 +17759,15 @@
       <c r="A126" s="97"/>
       <c r="B126" s="89"/>
       <c r="C126" s="108"/>
-      <c r="D126" s="152" t="str">
+      <c r="D126" s="241" t="str">
         <f>IF(B126="","",IFERROR(VLOOKUP(B126,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E126" s="153"/>
-      <c r="F126" s="153"/>
-      <c r="G126" s="153"/>
-      <c r="H126" s="153"/>
-      <c r="I126" s="154"/>
+      <c r="E126" s="242"/>
+      <c r="F126" s="242"/>
+      <c r="G126" s="242"/>
+      <c r="H126" s="242"/>
+      <c r="I126" s="243"/>
       <c r="J126" s="103"/>
       <c r="K126" s="138" t="str">
         <f>IF(B126="","",IFERROR(VLOOKUP(B126,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -17742,11 +17794,11 @@
         <v/>
       </c>
       <c r="T126" s="96"/>
-      <c r="U126" s="158" t="str">
+      <c r="U126" s="234" t="str">
         <f>IF(B126="","",IFERROR(VLOOKUP(B126,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V126" s="159"/>
+      <c r="V126" s="235"/>
       <c r="W126" s="73"/>
       <c r="X126" s="88"/>
       <c r="Y126" s="97"/>
@@ -17755,15 +17807,15 @@
       <c r="A127" s="97"/>
       <c r="B127" s="92"/>
       <c r="C127" s="109"/>
-      <c r="D127" s="149" t="str">
+      <c r="D127" s="238" t="str">
         <f>IF(B127="","",IFERROR(VLOOKUP(B127,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E127" s="150"/>
-      <c r="F127" s="150"/>
-      <c r="G127" s="150"/>
-      <c r="H127" s="150"/>
-      <c r="I127" s="151"/>
+      <c r="E127" s="239"/>
+      <c r="F127" s="239"/>
+      <c r="G127" s="239"/>
+      <c r="H127" s="239"/>
+      <c r="I127" s="240"/>
       <c r="J127" s="104"/>
       <c r="K127" s="140" t="str">
         <f>IF(B127="","",IFERROR(VLOOKUP(B127,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -17790,11 +17842,11 @@
         <v/>
       </c>
       <c r="T127" s="99"/>
-      <c r="U127" s="158" t="str">
+      <c r="U127" s="234" t="str">
         <f>IF(B127="","",IFERROR(VLOOKUP(B127,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V127" s="159"/>
+      <c r="V127" s="235"/>
       <c r="W127" s="73"/>
       <c r="X127" s="88"/>
       <c r="Y127" s="97"/>
@@ -17803,15 +17855,15 @@
       <c r="A128" s="97"/>
       <c r="B128" s="89"/>
       <c r="C128" s="108"/>
-      <c r="D128" s="152" t="str">
+      <c r="D128" s="241" t="str">
         <f>IF(B128="","",IFERROR(VLOOKUP(B128,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E128" s="153"/>
-      <c r="F128" s="153"/>
-      <c r="G128" s="153"/>
-      <c r="H128" s="153"/>
-      <c r="I128" s="154"/>
+      <c r="E128" s="242"/>
+      <c r="F128" s="242"/>
+      <c r="G128" s="242"/>
+      <c r="H128" s="242"/>
+      <c r="I128" s="243"/>
       <c r="J128" s="103"/>
       <c r="K128" s="138" t="str">
         <f>IF(B128="","",IFERROR(VLOOKUP(B128,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -17838,11 +17890,11 @@
         <v/>
       </c>
       <c r="T128" s="96"/>
-      <c r="U128" s="158" t="str">
+      <c r="U128" s="234" t="str">
         <f>IF(B128="","",IFERROR(VLOOKUP(B128,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V128" s="159"/>
+      <c r="V128" s="235"/>
       <c r="W128" s="73"/>
       <c r="X128" s="88"/>
       <c r="Y128" s="97"/>
@@ -17851,15 +17903,15 @@
       <c r="A129" s="97"/>
       <c r="B129" s="92"/>
       <c r="C129" s="109"/>
-      <c r="D129" s="149" t="str">
+      <c r="D129" s="238" t="str">
         <f>IF(B129="","",IFERROR(VLOOKUP(B129,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E129" s="150"/>
-      <c r="F129" s="150"/>
-      <c r="G129" s="150"/>
-      <c r="H129" s="150"/>
-      <c r="I129" s="151"/>
+      <c r="E129" s="239"/>
+      <c r="F129" s="239"/>
+      <c r="G129" s="239"/>
+      <c r="H129" s="239"/>
+      <c r="I129" s="240"/>
       <c r="J129" s="104"/>
       <c r="K129" s="140" t="str">
         <f>IF(B129="","",IFERROR(VLOOKUP(B129,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -17886,11 +17938,11 @@
         <v/>
       </c>
       <c r="T129" s="99"/>
-      <c r="U129" s="158" t="str">
+      <c r="U129" s="234" t="str">
         <f>IF(B129="","",IFERROR(VLOOKUP(B129,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V129" s="159"/>
+      <c r="V129" s="235"/>
       <c r="W129" s="73"/>
       <c r="X129" s="88"/>
       <c r="Y129" s="97"/>
@@ -17899,15 +17951,15 @@
       <c r="A130" s="97"/>
       <c r="B130" s="89"/>
       <c r="C130" s="108"/>
-      <c r="D130" s="152" t="str">
+      <c r="D130" s="241" t="str">
         <f>IF(B130="","",IFERROR(VLOOKUP(B130,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E130" s="153"/>
-      <c r="F130" s="153"/>
-      <c r="G130" s="153"/>
-      <c r="H130" s="153"/>
-      <c r="I130" s="154"/>
+      <c r="E130" s="242"/>
+      <c r="F130" s="242"/>
+      <c r="G130" s="242"/>
+      <c r="H130" s="242"/>
+      <c r="I130" s="243"/>
       <c r="J130" s="103"/>
       <c r="K130" s="138" t="str">
         <f>IF(B130="","",IFERROR(VLOOKUP(B130,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -17934,11 +17986,11 @@
         <v/>
       </c>
       <c r="T130" s="96"/>
-      <c r="U130" s="158" t="str">
+      <c r="U130" s="234" t="str">
         <f>IF(B130="","",IFERROR(VLOOKUP(B130,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V130" s="159"/>
+      <c r="V130" s="235"/>
       <c r="W130" s="73"/>
       <c r="X130" s="88"/>
       <c r="Y130" s="97"/>
@@ -17947,15 +17999,15 @@
       <c r="A131" s="97"/>
       <c r="B131" s="92"/>
       <c r="C131" s="109"/>
-      <c r="D131" s="149" t="str">
+      <c r="D131" s="238" t="str">
         <f>IF(B131="","",IFERROR(VLOOKUP(B131,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E131" s="150"/>
-      <c r="F131" s="150"/>
-      <c r="G131" s="150"/>
-      <c r="H131" s="150"/>
-      <c r="I131" s="151"/>
+      <c r="E131" s="239"/>
+      <c r="F131" s="239"/>
+      <c r="G131" s="239"/>
+      <c r="H131" s="239"/>
+      <c r="I131" s="240"/>
       <c r="J131" s="104"/>
       <c r="K131" s="140" t="str">
         <f>IF(B131="","",IFERROR(VLOOKUP(B131,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -17982,11 +18034,11 @@
         <v/>
       </c>
       <c r="T131" s="99"/>
-      <c r="U131" s="158" t="str">
+      <c r="U131" s="234" t="str">
         <f>IF(B131="","",IFERROR(VLOOKUP(B131,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V131" s="159"/>
+      <c r="V131" s="235"/>
       <c r="W131" s="73"/>
       <c r="X131" s="88"/>
       <c r="Y131" s="97"/>
@@ -17995,15 +18047,15 @@
       <c r="A132" s="97"/>
       <c r="B132" s="89"/>
       <c r="C132" s="108"/>
-      <c r="D132" s="152" t="str">
+      <c r="D132" s="241" t="str">
         <f>IF(B132="","",IFERROR(VLOOKUP(B132,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E132" s="153"/>
-      <c r="F132" s="153"/>
-      <c r="G132" s="153"/>
-      <c r="H132" s="153"/>
-      <c r="I132" s="154"/>
+      <c r="E132" s="242"/>
+      <c r="F132" s="242"/>
+      <c r="G132" s="242"/>
+      <c r="H132" s="242"/>
+      <c r="I132" s="243"/>
       <c r="J132" s="103"/>
       <c r="K132" s="138" t="str">
         <f>IF(B132="","",IFERROR(VLOOKUP(B132,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -18030,11 +18082,11 @@
         <v/>
       </c>
       <c r="T132" s="96"/>
-      <c r="U132" s="158" t="str">
+      <c r="U132" s="234" t="str">
         <f>IF(B132="","",IFERROR(VLOOKUP(B132,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V132" s="159"/>
+      <c r="V132" s="235"/>
       <c r="W132" s="73"/>
       <c r="X132" s="88"/>
       <c r="Y132" s="97"/>
@@ -18043,15 +18095,15 @@
       <c r="A133" s="97"/>
       <c r="B133" s="92"/>
       <c r="C133" s="109"/>
-      <c r="D133" s="149" t="str">
+      <c r="D133" s="238" t="str">
         <f>IF(B133="","",IFERROR(VLOOKUP(B133,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E133" s="150"/>
-      <c r="F133" s="150"/>
-      <c r="G133" s="150"/>
-      <c r="H133" s="150"/>
-      <c r="I133" s="151"/>
+      <c r="E133" s="239"/>
+      <c r="F133" s="239"/>
+      <c r="G133" s="239"/>
+      <c r="H133" s="239"/>
+      <c r="I133" s="240"/>
       <c r="J133" s="104"/>
       <c r="K133" s="140" t="str">
         <f>IF(B133="","",IFERROR(VLOOKUP(B133,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -18078,11 +18130,11 @@
         <v/>
       </c>
       <c r="T133" s="99"/>
-      <c r="U133" s="158" t="str">
+      <c r="U133" s="234" t="str">
         <f>IF(B133="","",IFERROR(VLOOKUP(B133,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V133" s="159"/>
+      <c r="V133" s="235"/>
       <c r="W133" s="73"/>
       <c r="X133" s="88"/>
       <c r="Y133" s="97"/>
@@ -18091,15 +18143,15 @@
       <c r="A134" s="97"/>
       <c r="B134" s="89"/>
       <c r="C134" s="108"/>
-      <c r="D134" s="152" t="str">
+      <c r="D134" s="241" t="str">
         <f>IF(B134="","",IFERROR(VLOOKUP(B134,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E134" s="153"/>
-      <c r="F134" s="153"/>
-      <c r="G134" s="153"/>
-      <c r="H134" s="153"/>
-      <c r="I134" s="154"/>
+      <c r="E134" s="242"/>
+      <c r="F134" s="242"/>
+      <c r="G134" s="242"/>
+      <c r="H134" s="242"/>
+      <c r="I134" s="243"/>
       <c r="J134" s="103"/>
       <c r="K134" s="138" t="str">
         <f>IF(B134="","",IFERROR(VLOOKUP(B134,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -18126,11 +18178,11 @@
         <v/>
       </c>
       <c r="T134" s="96"/>
-      <c r="U134" s="158" t="str">
+      <c r="U134" s="234" t="str">
         <f>IF(B134="","",IFERROR(VLOOKUP(B134,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V134" s="159"/>
+      <c r="V134" s="235"/>
       <c r="W134" s="73"/>
       <c r="X134" s="88"/>
       <c r="Y134" s="97"/>
@@ -18139,15 +18191,15 @@
       <c r="A135" s="97"/>
       <c r="B135" s="92"/>
       <c r="C135" s="109"/>
-      <c r="D135" s="149" t="str">
+      <c r="D135" s="238" t="str">
         <f>IF(B135="","",IFERROR(VLOOKUP(B135,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E135" s="150"/>
-      <c r="F135" s="150"/>
-      <c r="G135" s="150"/>
-      <c r="H135" s="150"/>
-      <c r="I135" s="151"/>
+      <c r="E135" s="239"/>
+      <c r="F135" s="239"/>
+      <c r="G135" s="239"/>
+      <c r="H135" s="239"/>
+      <c r="I135" s="240"/>
       <c r="J135" s="104"/>
       <c r="K135" s="140" t="str">
         <f>IF(B135="","",IFERROR(VLOOKUP(B135,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -18174,11 +18226,11 @@
         <v/>
       </c>
       <c r="T135" s="99"/>
-      <c r="U135" s="158" t="str">
+      <c r="U135" s="234" t="str">
         <f>IF(B135="","",IFERROR(VLOOKUP(B135,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V135" s="159"/>
+      <c r="V135" s="235"/>
       <c r="W135" s="73"/>
       <c r="X135" s="88"/>
       <c r="Y135" s="97"/>
@@ -18187,15 +18239,15 @@
       <c r="A136" s="97"/>
       <c r="B136" s="89"/>
       <c r="C136" s="108"/>
-      <c r="D136" s="152" t="str">
+      <c r="D136" s="241" t="str">
         <f>IF(B136="","",IFERROR(VLOOKUP(B136,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E136" s="153"/>
-      <c r="F136" s="153"/>
-      <c r="G136" s="153"/>
-      <c r="H136" s="153"/>
-      <c r="I136" s="154"/>
+      <c r="E136" s="242"/>
+      <c r="F136" s="242"/>
+      <c r="G136" s="242"/>
+      <c r="H136" s="242"/>
+      <c r="I136" s="243"/>
       <c r="J136" s="103"/>
       <c r="K136" s="138" t="str">
         <f>IF(B136="","",IFERROR(VLOOKUP(B136,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -18222,11 +18274,11 @@
         <v/>
       </c>
       <c r="T136" s="96"/>
-      <c r="U136" s="158" t="str">
+      <c r="U136" s="234" t="str">
         <f>IF(B136="","",IFERROR(VLOOKUP(B136,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V136" s="159"/>
+      <c r="V136" s="235"/>
       <c r="W136" s="73"/>
       <c r="X136" s="88"/>
       <c r="Y136" s="97"/>
@@ -18235,15 +18287,15 @@
       <c r="A137" s="97"/>
       <c r="B137" s="92"/>
       <c r="C137" s="109"/>
-      <c r="D137" s="149" t="str">
+      <c r="D137" s="238" t="str">
         <f>IF(B137="","",IFERROR(VLOOKUP(B137,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E137" s="150"/>
-      <c r="F137" s="150"/>
-      <c r="G137" s="150"/>
-      <c r="H137" s="150"/>
-      <c r="I137" s="151"/>
+      <c r="E137" s="239"/>
+      <c r="F137" s="239"/>
+      <c r="G137" s="239"/>
+      <c r="H137" s="239"/>
+      <c r="I137" s="240"/>
       <c r="J137" s="104"/>
       <c r="K137" s="140" t="str">
         <f>IF(B137="","",IFERROR(VLOOKUP(B137,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -18270,11 +18322,11 @@
         <v/>
       </c>
       <c r="T137" s="99"/>
-      <c r="U137" s="158" t="str">
+      <c r="U137" s="234" t="str">
         <f>IF(B137="","",IFERROR(VLOOKUP(B137,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V137" s="159"/>
+      <c r="V137" s="235"/>
       <c r="W137" s="73"/>
       <c r="X137" s="88"/>
       <c r="Y137" s="97"/>
@@ -18283,15 +18335,15 @@
       <c r="A138" s="97"/>
       <c r="B138" s="89"/>
       <c r="C138" s="108"/>
-      <c r="D138" s="152" t="str">
+      <c r="D138" s="241" t="str">
         <f>IF(B138="","",IFERROR(VLOOKUP(B138,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E138" s="153"/>
-      <c r="F138" s="153"/>
-      <c r="G138" s="153"/>
-      <c r="H138" s="153"/>
-      <c r="I138" s="154"/>
+      <c r="E138" s="242"/>
+      <c r="F138" s="242"/>
+      <c r="G138" s="242"/>
+      <c r="H138" s="242"/>
+      <c r="I138" s="243"/>
       <c r="J138" s="103"/>
       <c r="K138" s="138" t="str">
         <f>IF(B138="","",IFERROR(VLOOKUP(B138,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -18318,11 +18370,11 @@
         <v/>
       </c>
       <c r="T138" s="96"/>
-      <c r="U138" s="158" t="str">
+      <c r="U138" s="234" t="str">
         <f>IF(B138="","",IFERROR(VLOOKUP(B138,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V138" s="159"/>
+      <c r="V138" s="235"/>
       <c r="W138" s="73"/>
       <c r="X138" s="88"/>
       <c r="Y138" s="97"/>
@@ -18331,15 +18383,15 @@
       <c r="A139" s="97"/>
       <c r="B139" s="92"/>
       <c r="C139" s="109"/>
-      <c r="D139" s="149" t="str">
+      <c r="D139" s="238" t="str">
         <f>IF(B139="","",IFERROR(VLOOKUP(B139,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E139" s="150"/>
-      <c r="F139" s="150"/>
-      <c r="G139" s="150"/>
-      <c r="H139" s="150"/>
-      <c r="I139" s="151"/>
+      <c r="E139" s="239"/>
+      <c r="F139" s="239"/>
+      <c r="G139" s="239"/>
+      <c r="H139" s="239"/>
+      <c r="I139" s="240"/>
       <c r="J139" s="104"/>
       <c r="K139" s="140" t="str">
         <f>IF(B139="","",IFERROR(VLOOKUP(B139,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -18366,11 +18418,11 @@
         <v/>
       </c>
       <c r="T139" s="99"/>
-      <c r="U139" s="158" t="str">
+      <c r="U139" s="234" t="str">
         <f>IF(B139="","",IFERROR(VLOOKUP(B139,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V139" s="159"/>
+      <c r="V139" s="235"/>
       <c r="W139" s="73"/>
       <c r="X139" s="88"/>
       <c r="Y139" s="97"/>
@@ -18379,15 +18431,15 @@
       <c r="A140" s="97"/>
       <c r="B140" s="89"/>
       <c r="C140" s="108"/>
-      <c r="D140" s="152" t="str">
+      <c r="D140" s="241" t="str">
         <f>IF(B140="","",IFERROR(VLOOKUP(B140,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E140" s="153"/>
-      <c r="F140" s="153"/>
-      <c r="G140" s="153"/>
-      <c r="H140" s="153"/>
-      <c r="I140" s="154"/>
+      <c r="E140" s="242"/>
+      <c r="F140" s="242"/>
+      <c r="G140" s="242"/>
+      <c r="H140" s="242"/>
+      <c r="I140" s="243"/>
       <c r="J140" s="103"/>
       <c r="K140" s="138" t="str">
         <f>IF(B140="","",IFERROR(VLOOKUP(B140,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -18414,11 +18466,11 @@
         <v/>
       </c>
       <c r="T140" s="96"/>
-      <c r="U140" s="158" t="str">
+      <c r="U140" s="234" t="str">
         <f>IF(B140="","",IFERROR(VLOOKUP(B140,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V140" s="159"/>
+      <c r="V140" s="235"/>
       <c r="W140" s="73"/>
       <c r="X140" s="88"/>
       <c r="Y140" s="97"/>
@@ -18427,15 +18479,15 @@
       <c r="A141" s="97"/>
       <c r="B141" s="92"/>
       <c r="C141" s="109"/>
-      <c r="D141" s="149" t="str">
+      <c r="D141" s="238" t="str">
         <f>IF(B141="","",IFERROR(VLOOKUP(B141,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E141" s="150"/>
-      <c r="F141" s="150"/>
-      <c r="G141" s="150"/>
-      <c r="H141" s="150"/>
-      <c r="I141" s="151"/>
+      <c r="E141" s="239"/>
+      <c r="F141" s="239"/>
+      <c r="G141" s="239"/>
+      <c r="H141" s="239"/>
+      <c r="I141" s="240"/>
       <c r="J141" s="104"/>
       <c r="K141" s="140" t="str">
         <f>IF(B141="","",IFERROR(VLOOKUP(B141,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -18462,11 +18514,11 @@
         <v/>
       </c>
       <c r="T141" s="99"/>
-      <c r="U141" s="158" t="str">
+      <c r="U141" s="234" t="str">
         <f>IF(B141="","",IFERROR(VLOOKUP(B141,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V141" s="159"/>
+      <c r="V141" s="235"/>
       <c r="W141" s="73"/>
       <c r="X141" s="88"/>
       <c r="Y141" s="97"/>
@@ -18475,15 +18527,15 @@
       <c r="A142" s="97"/>
       <c r="B142" s="89"/>
       <c r="C142" s="108"/>
-      <c r="D142" s="152" t="str">
+      <c r="D142" s="241" t="str">
         <f>IF(B142="","",IFERROR(VLOOKUP(B142,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E142" s="153"/>
-      <c r="F142" s="153"/>
-      <c r="G142" s="153"/>
-      <c r="H142" s="153"/>
-      <c r="I142" s="154"/>
+      <c r="E142" s="242"/>
+      <c r="F142" s="242"/>
+      <c r="G142" s="242"/>
+      <c r="H142" s="242"/>
+      <c r="I142" s="243"/>
       <c r="J142" s="103"/>
       <c r="K142" s="138" t="str">
         <f>IF(B142="","",IFERROR(VLOOKUP(B142,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -18510,11 +18562,11 @@
         <v/>
       </c>
       <c r="T142" s="96"/>
-      <c r="U142" s="158" t="str">
+      <c r="U142" s="234" t="str">
         <f>IF(B142="","",IFERROR(VLOOKUP(B142,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V142" s="159"/>
+      <c r="V142" s="235"/>
       <c r="W142" s="73"/>
       <c r="X142" s="88"/>
       <c r="Y142" s="97"/>
@@ -18523,15 +18575,15 @@
       <c r="A143" s="97"/>
       <c r="B143" s="92"/>
       <c r="C143" s="109"/>
-      <c r="D143" s="149" t="str">
+      <c r="D143" s="238" t="str">
         <f>IF(B143="","",IFERROR(VLOOKUP(B143,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E143" s="150"/>
-      <c r="F143" s="150"/>
-      <c r="G143" s="150"/>
-      <c r="H143" s="150"/>
-      <c r="I143" s="151"/>
+      <c r="E143" s="239"/>
+      <c r="F143" s="239"/>
+      <c r="G143" s="239"/>
+      <c r="H143" s="239"/>
+      <c r="I143" s="240"/>
       <c r="J143" s="104"/>
       <c r="K143" s="140" t="str">
         <f>IF(B143="","",IFERROR(VLOOKUP(B143,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -18558,11 +18610,11 @@
         <v/>
       </c>
       <c r="T143" s="99"/>
-      <c r="U143" s="158" t="str">
+      <c r="U143" s="234" t="str">
         <f>IF(B143="","",IFERROR(VLOOKUP(B143,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V143" s="159"/>
+      <c r="V143" s="235"/>
       <c r="W143" s="73"/>
       <c r="X143" s="88"/>
       <c r="Y143" s="97"/>
@@ -18571,15 +18623,15 @@
       <c r="A144" s="97"/>
       <c r="B144" s="89"/>
       <c r="C144" s="108"/>
-      <c r="D144" s="152" t="str">
+      <c r="D144" s="241" t="str">
         <f>IF(B144="","",IFERROR(VLOOKUP(B144,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E144" s="153"/>
-      <c r="F144" s="153"/>
-      <c r="G144" s="153"/>
-      <c r="H144" s="153"/>
-      <c r="I144" s="154"/>
+      <c r="E144" s="242"/>
+      <c r="F144" s="242"/>
+      <c r="G144" s="242"/>
+      <c r="H144" s="242"/>
+      <c r="I144" s="243"/>
       <c r="J144" s="103"/>
       <c r="K144" s="138" t="str">
         <f>IF(B144="","",IFERROR(VLOOKUP(B144,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -18606,11 +18658,11 @@
         <v/>
       </c>
       <c r="T144" s="96"/>
-      <c r="U144" s="158" t="str">
+      <c r="U144" s="234" t="str">
         <f>IF(B144="","",IFERROR(VLOOKUP(B144,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V144" s="159"/>
+      <c r="V144" s="235"/>
       <c r="W144" s="73"/>
       <c r="X144" s="88"/>
       <c r="Y144" s="97"/>
@@ -18619,15 +18671,15 @@
       <c r="A145" s="97"/>
       <c r="B145" s="92"/>
       <c r="C145" s="109"/>
-      <c r="D145" s="149" t="str">
+      <c r="D145" s="238" t="str">
         <f>IF(B145="","",IFERROR(VLOOKUP(B145,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E145" s="150"/>
-      <c r="F145" s="150"/>
-      <c r="G145" s="150"/>
-      <c r="H145" s="150"/>
-      <c r="I145" s="151"/>
+      <c r="E145" s="239"/>
+      <c r="F145" s="239"/>
+      <c r="G145" s="239"/>
+      <c r="H145" s="239"/>
+      <c r="I145" s="240"/>
       <c r="J145" s="104"/>
       <c r="K145" s="140" t="str">
         <f>IF(B145="","",IFERROR(VLOOKUP(B145,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -18654,11 +18706,11 @@
         <v/>
       </c>
       <c r="T145" s="99"/>
-      <c r="U145" s="158" t="str">
+      <c r="U145" s="234" t="str">
         <f>IF(B145="","",IFERROR(VLOOKUP(B145,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V145" s="159"/>
+      <c r="V145" s="235"/>
       <c r="W145" s="73"/>
       <c r="X145" s="88"/>
       <c r="Y145" s="97"/>
@@ -18667,15 +18719,15 @@
       <c r="A146" s="97"/>
       <c r="B146" s="89"/>
       <c r="C146" s="108"/>
-      <c r="D146" s="152" t="str">
+      <c r="D146" s="241" t="str">
         <f>IF(B146="","",IFERROR(VLOOKUP(B146,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E146" s="153"/>
-      <c r="F146" s="153"/>
-      <c r="G146" s="153"/>
-      <c r="H146" s="153"/>
-      <c r="I146" s="154"/>
+      <c r="E146" s="242"/>
+      <c r="F146" s="242"/>
+      <c r="G146" s="242"/>
+      <c r="H146" s="242"/>
+      <c r="I146" s="243"/>
       <c r="J146" s="103"/>
       <c r="K146" s="138" t="str">
         <f>IF(B146="","",IFERROR(VLOOKUP(B146,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -18702,11 +18754,11 @@
         <v/>
       </c>
       <c r="T146" s="96"/>
-      <c r="U146" s="158" t="str">
+      <c r="U146" s="234" t="str">
         <f>IF(B146="","",IFERROR(VLOOKUP(B146,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V146" s="159"/>
+      <c r="V146" s="235"/>
       <c r="W146" s="73"/>
       <c r="X146" s="88"/>
       <c r="Y146" s="97"/>
@@ -18715,15 +18767,15 @@
       <c r="A147" s="97"/>
       <c r="B147" s="92"/>
       <c r="C147" s="109"/>
-      <c r="D147" s="149" t="str">
+      <c r="D147" s="238" t="str">
         <f>IF(B147="","",IFERROR(VLOOKUP(B147,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E147" s="150"/>
-      <c r="F147" s="150"/>
-      <c r="G147" s="150"/>
-      <c r="H147" s="150"/>
-      <c r="I147" s="151"/>
+      <c r="E147" s="239"/>
+      <c r="F147" s="239"/>
+      <c r="G147" s="239"/>
+      <c r="H147" s="239"/>
+      <c r="I147" s="240"/>
       <c r="J147" s="104"/>
       <c r="K147" s="140" t="str">
         <f>IF(B147="","",IFERROR(VLOOKUP(B147,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -18750,11 +18802,11 @@
         <v/>
       </c>
       <c r="T147" s="99"/>
-      <c r="U147" s="158" t="str">
+      <c r="U147" s="234" t="str">
         <f>IF(B147="","",IFERROR(VLOOKUP(B147,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V147" s="159"/>
+      <c r="V147" s="235"/>
       <c r="W147" s="73"/>
       <c r="X147" s="88"/>
       <c r="Y147" s="97"/>
@@ -18763,15 +18815,15 @@
       <c r="A148" s="97"/>
       <c r="B148" s="89"/>
       <c r="C148" s="108"/>
-      <c r="D148" s="152" t="str">
+      <c r="D148" s="241" t="str">
         <f>IF(B148="","",IFERROR(VLOOKUP(B148,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E148" s="153"/>
-      <c r="F148" s="153"/>
-      <c r="G148" s="153"/>
-      <c r="H148" s="153"/>
-      <c r="I148" s="154"/>
+      <c r="E148" s="242"/>
+      <c r="F148" s="242"/>
+      <c r="G148" s="242"/>
+      <c r="H148" s="242"/>
+      <c r="I148" s="243"/>
       <c r="J148" s="103"/>
       <c r="K148" s="138" t="str">
         <f>IF(B148="","",IFERROR(VLOOKUP(B148,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -18798,11 +18850,11 @@
         <v/>
       </c>
       <c r="T148" s="96"/>
-      <c r="U148" s="158" t="str">
+      <c r="U148" s="234" t="str">
         <f>IF(B148="","",IFERROR(VLOOKUP(B148,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V148" s="159"/>
+      <c r="V148" s="235"/>
       <c r="W148" s="73"/>
       <c r="X148" s="88"/>
       <c r="Y148" s="97"/>
@@ -18811,15 +18863,15 @@
       <c r="A149" s="97"/>
       <c r="B149" s="92"/>
       <c r="C149" s="109"/>
-      <c r="D149" s="149" t="str">
+      <c r="D149" s="238" t="str">
         <f>IF(B149="","",IFERROR(VLOOKUP(B149,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E149" s="150"/>
-      <c r="F149" s="150"/>
-      <c r="G149" s="150"/>
-      <c r="H149" s="150"/>
-      <c r="I149" s="151"/>
+      <c r="E149" s="239"/>
+      <c r="F149" s="239"/>
+      <c r="G149" s="239"/>
+      <c r="H149" s="239"/>
+      <c r="I149" s="240"/>
       <c r="J149" s="104"/>
       <c r="K149" s="140" t="str">
         <f>IF(B149="","",IFERROR(VLOOKUP(B149,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -18846,11 +18898,11 @@
         <v/>
       </c>
       <c r="T149" s="99"/>
-      <c r="U149" s="158" t="str">
+      <c r="U149" s="234" t="str">
         <f>IF(B149="","",IFERROR(VLOOKUP(B149,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V149" s="159"/>
+      <c r="V149" s="235"/>
       <c r="W149" s="73"/>
       <c r="X149" s="88"/>
       <c r="Y149" s="97"/>
@@ -18859,15 +18911,15 @@
       <c r="A150" s="97"/>
       <c r="B150" s="89"/>
       <c r="C150" s="108"/>
-      <c r="D150" s="152" t="str">
+      <c r="D150" s="241" t="str">
         <f>IF(B150="","",IFERROR(VLOOKUP(B150,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E150" s="153"/>
-      <c r="F150" s="153"/>
-      <c r="G150" s="153"/>
-      <c r="H150" s="153"/>
-      <c r="I150" s="154"/>
+      <c r="E150" s="242"/>
+      <c r="F150" s="242"/>
+      <c r="G150" s="242"/>
+      <c r="H150" s="242"/>
+      <c r="I150" s="243"/>
       <c r="J150" s="103"/>
       <c r="K150" s="138" t="str">
         <f>IF(B150="","",IFERROR(VLOOKUP(B150,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -18894,11 +18946,11 @@
         <v/>
       </c>
       <c r="T150" s="96"/>
-      <c r="U150" s="158" t="str">
+      <c r="U150" s="234" t="str">
         <f>IF(B150="","",IFERROR(VLOOKUP(B150,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V150" s="159"/>
+      <c r="V150" s="235"/>
       <c r="W150" s="73"/>
       <c r="X150" s="88"/>
       <c r="Y150" s="97"/>
@@ -18907,15 +18959,15 @@
       <c r="A151" s="97"/>
       <c r="B151" s="92"/>
       <c r="C151" s="109"/>
-      <c r="D151" s="149" t="str">
+      <c r="D151" s="238" t="str">
         <f>IF(B151="","",IFERROR(VLOOKUP(B151,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E151" s="150"/>
-      <c r="F151" s="150"/>
-      <c r="G151" s="150"/>
-      <c r="H151" s="150"/>
-      <c r="I151" s="151"/>
+      <c r="E151" s="239"/>
+      <c r="F151" s="239"/>
+      <c r="G151" s="239"/>
+      <c r="H151" s="239"/>
+      <c r="I151" s="240"/>
       <c r="J151" s="104"/>
       <c r="K151" s="140" t="str">
         <f>IF(B151="","",IFERROR(VLOOKUP(B151,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -18942,11 +18994,11 @@
         <v/>
       </c>
       <c r="T151" s="99"/>
-      <c r="U151" s="158" t="str">
+      <c r="U151" s="234" t="str">
         <f>IF(B151="","",IFERROR(VLOOKUP(B151,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V151" s="159"/>
+      <c r="V151" s="235"/>
       <c r="W151" s="73"/>
       <c r="X151" s="88"/>
       <c r="Y151" s="97"/>
@@ -18955,15 +19007,15 @@
       <c r="A152" s="97"/>
       <c r="B152" s="89"/>
       <c r="C152" s="108"/>
-      <c r="D152" s="152" t="str">
+      <c r="D152" s="241" t="str">
         <f>IF(B152="","",IFERROR(VLOOKUP(B152,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E152" s="153"/>
-      <c r="F152" s="153"/>
-      <c r="G152" s="153"/>
-      <c r="H152" s="153"/>
-      <c r="I152" s="154"/>
+      <c r="E152" s="242"/>
+      <c r="F152" s="242"/>
+      <c r="G152" s="242"/>
+      <c r="H152" s="242"/>
+      <c r="I152" s="243"/>
       <c r="J152" s="103"/>
       <c r="K152" s="138" t="str">
         <f>IF(B152="","",IFERROR(VLOOKUP(B152,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -18990,11 +19042,11 @@
         <v/>
       </c>
       <c r="T152" s="96"/>
-      <c r="U152" s="158" t="str">
+      <c r="U152" s="234" t="str">
         <f>IF(B152="","",IFERROR(VLOOKUP(B152,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V152" s="159"/>
+      <c r="V152" s="235"/>
       <c r="W152" s="73"/>
       <c r="X152" s="88"/>
       <c r="Y152" s="97"/>
@@ -19003,15 +19055,15 @@
       <c r="A153" s="97"/>
       <c r="B153" s="92"/>
       <c r="C153" s="109"/>
-      <c r="D153" s="149" t="str">
+      <c r="D153" s="238" t="str">
         <f>IF(B153="","",IFERROR(VLOOKUP(B153,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E153" s="150"/>
-      <c r="F153" s="150"/>
-      <c r="G153" s="150"/>
-      <c r="H153" s="150"/>
-      <c r="I153" s="151"/>
+      <c r="E153" s="239"/>
+      <c r="F153" s="239"/>
+      <c r="G153" s="239"/>
+      <c r="H153" s="239"/>
+      <c r="I153" s="240"/>
       <c r="J153" s="104"/>
       <c r="K153" s="140" t="str">
         <f>IF(B153="","",IFERROR(VLOOKUP(B153,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -19038,11 +19090,11 @@
         <v/>
       </c>
       <c r="T153" s="99"/>
-      <c r="U153" s="158" t="str">
+      <c r="U153" s="234" t="str">
         <f>IF(B153="","",IFERROR(VLOOKUP(B153,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V153" s="159"/>
+      <c r="V153" s="235"/>
       <c r="W153" s="73"/>
       <c r="X153" s="88"/>
       <c r="Y153" s="97"/>
@@ -19051,15 +19103,15 @@
       <c r="A154" s="97"/>
       <c r="B154" s="89"/>
       <c r="C154" s="108"/>
-      <c r="D154" s="152" t="str">
+      <c r="D154" s="241" t="str">
         <f>IF(B154="","",IFERROR(VLOOKUP(B154,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E154" s="153"/>
-      <c r="F154" s="153"/>
-      <c r="G154" s="153"/>
-      <c r="H154" s="153"/>
-      <c r="I154" s="154"/>
+      <c r="E154" s="242"/>
+      <c r="F154" s="242"/>
+      <c r="G154" s="242"/>
+      <c r="H154" s="242"/>
+      <c r="I154" s="243"/>
       <c r="J154" s="103"/>
       <c r="K154" s="138" t="str">
         <f>IF(B154="","",IFERROR(VLOOKUP(B154,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -19086,11 +19138,11 @@
         <v/>
       </c>
       <c r="T154" s="96"/>
-      <c r="U154" s="158" t="str">
+      <c r="U154" s="234" t="str">
         <f>IF(B154="","",IFERROR(VLOOKUP(B154,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V154" s="159"/>
+      <c r="V154" s="235"/>
       <c r="W154" s="73"/>
       <c r="X154" s="88"/>
       <c r="Y154" s="97"/>
@@ -19099,15 +19151,15 @@
       <c r="A155" s="97"/>
       <c r="B155" s="92"/>
       <c r="C155" s="109"/>
-      <c r="D155" s="149" t="str">
+      <c r="D155" s="238" t="str">
         <f>IF(B155="","",IFERROR(VLOOKUP(B155,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E155" s="150"/>
-      <c r="F155" s="150"/>
-      <c r="G155" s="150"/>
-      <c r="H155" s="150"/>
-      <c r="I155" s="151"/>
+      <c r="E155" s="239"/>
+      <c r="F155" s="239"/>
+      <c r="G155" s="239"/>
+      <c r="H155" s="239"/>
+      <c r="I155" s="240"/>
       <c r="J155" s="104"/>
       <c r="K155" s="140" t="str">
         <f>IF(B155="","",IFERROR(VLOOKUP(B155,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -19134,11 +19186,11 @@
         <v/>
       </c>
       <c r="T155" s="99"/>
-      <c r="U155" s="158" t="str">
+      <c r="U155" s="234" t="str">
         <f>IF(B155="","",IFERROR(VLOOKUP(B155,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V155" s="159"/>
+      <c r="V155" s="235"/>
       <c r="W155" s="73"/>
       <c r="X155" s="88"/>
       <c r="Y155" s="97"/>
@@ -19147,15 +19199,15 @@
       <c r="A156" s="97"/>
       <c r="B156" s="89"/>
       <c r="C156" s="108"/>
-      <c r="D156" s="152" t="str">
+      <c r="D156" s="241" t="str">
         <f>IF(B156="","",IFERROR(VLOOKUP(B156,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E156" s="153"/>
-      <c r="F156" s="153"/>
-      <c r="G156" s="153"/>
-      <c r="H156" s="153"/>
-      <c r="I156" s="154"/>
+      <c r="E156" s="242"/>
+      <c r="F156" s="242"/>
+      <c r="G156" s="242"/>
+      <c r="H156" s="242"/>
+      <c r="I156" s="243"/>
       <c r="J156" s="103"/>
       <c r="K156" s="138" t="str">
         <f>IF(B156="","",IFERROR(VLOOKUP(B156,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -19182,11 +19234,11 @@
         <v/>
       </c>
       <c r="T156" s="96"/>
-      <c r="U156" s="158" t="str">
+      <c r="U156" s="234" t="str">
         <f>IF(B156="","",IFERROR(VLOOKUP(B156,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V156" s="159"/>
+      <c r="V156" s="235"/>
       <c r="W156" s="73"/>
       <c r="X156" s="88"/>
       <c r="Y156" s="97"/>
@@ -19195,15 +19247,15 @@
       <c r="A157" s="97"/>
       <c r="B157" s="92"/>
       <c r="C157" s="109"/>
-      <c r="D157" s="149" t="str">
+      <c r="D157" s="238" t="str">
         <f>IF(B157="","",IFERROR(VLOOKUP(B157,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E157" s="150"/>
-      <c r="F157" s="150"/>
-      <c r="G157" s="150"/>
-      <c r="H157" s="150"/>
-      <c r="I157" s="151"/>
+      <c r="E157" s="239"/>
+      <c r="F157" s="239"/>
+      <c r="G157" s="239"/>
+      <c r="H157" s="239"/>
+      <c r="I157" s="240"/>
       <c r="J157" s="104"/>
       <c r="K157" s="140" t="str">
         <f>IF(B157="","",IFERROR(VLOOKUP(B157,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -19230,11 +19282,11 @@
         <v/>
       </c>
       <c r="T157" s="99"/>
-      <c r="U157" s="158" t="str">
+      <c r="U157" s="234" t="str">
         <f>IF(B157="","",IFERROR(VLOOKUP(B157,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V157" s="159"/>
+      <c r="V157" s="235"/>
       <c r="W157" s="73"/>
       <c r="X157" s="88"/>
       <c r="Y157" s="97"/>
@@ -19243,15 +19295,15 @@
       <c r="A158" s="97"/>
       <c r="B158" s="89"/>
       <c r="C158" s="108"/>
-      <c r="D158" s="152" t="str">
+      <c r="D158" s="241" t="str">
         <f>IF(B158="","",IFERROR(VLOOKUP(B158,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E158" s="153"/>
-      <c r="F158" s="153"/>
-      <c r="G158" s="153"/>
-      <c r="H158" s="153"/>
-      <c r="I158" s="154"/>
+      <c r="E158" s="242"/>
+      <c r="F158" s="242"/>
+      <c r="G158" s="242"/>
+      <c r="H158" s="242"/>
+      <c r="I158" s="243"/>
       <c r="J158" s="103"/>
       <c r="K158" s="138" t="str">
         <f>IF(B158="","",IFERROR(VLOOKUP(B158,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -19278,11 +19330,11 @@
         <v/>
       </c>
       <c r="T158" s="96"/>
-      <c r="U158" s="158" t="str">
+      <c r="U158" s="234" t="str">
         <f>IF(B158="","",IFERROR(VLOOKUP(B158,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V158" s="159"/>
+      <c r="V158" s="235"/>
       <c r="W158" s="73"/>
       <c r="X158" s="88"/>
       <c r="Y158" s="97"/>
@@ -19291,15 +19343,15 @@
       <c r="A159" s="97"/>
       <c r="B159" s="92"/>
       <c r="C159" s="109"/>
-      <c r="D159" s="149" t="str">
+      <c r="D159" s="238" t="str">
         <f>IF(B159="","",IFERROR(VLOOKUP(B159,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E159" s="150"/>
-      <c r="F159" s="150"/>
-      <c r="G159" s="150"/>
-      <c r="H159" s="150"/>
-      <c r="I159" s="151"/>
+      <c r="E159" s="239"/>
+      <c r="F159" s="239"/>
+      <c r="G159" s="239"/>
+      <c r="H159" s="239"/>
+      <c r="I159" s="240"/>
       <c r="J159" s="104"/>
       <c r="K159" s="140" t="str">
         <f>IF(B159="","",IFERROR(VLOOKUP(B159,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -19326,11 +19378,11 @@
         <v/>
       </c>
       <c r="T159" s="99"/>
-      <c r="U159" s="158" t="str">
+      <c r="U159" s="234" t="str">
         <f>IF(B159="","",IFERROR(VLOOKUP(B159,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V159" s="159"/>
+      <c r="V159" s="235"/>
       <c r="W159" s="73"/>
       <c r="X159" s="88"/>
       <c r="Y159" s="97"/>
@@ -19339,15 +19391,15 @@
       <c r="A160" s="97"/>
       <c r="B160" s="89"/>
       <c r="C160" s="108"/>
-      <c r="D160" s="152" t="str">
+      <c r="D160" s="241" t="str">
         <f>IF(B160="","",IFERROR(VLOOKUP(B160,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E160" s="153"/>
-      <c r="F160" s="153"/>
-      <c r="G160" s="153"/>
-      <c r="H160" s="153"/>
-      <c r="I160" s="154"/>
+      <c r="E160" s="242"/>
+      <c r="F160" s="242"/>
+      <c r="G160" s="242"/>
+      <c r="H160" s="242"/>
+      <c r="I160" s="243"/>
       <c r="J160" s="103"/>
       <c r="K160" s="138" t="str">
         <f>IF(B160="","",IFERROR(VLOOKUP(B160,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -19374,11 +19426,11 @@
         <v/>
       </c>
       <c r="T160" s="96"/>
-      <c r="U160" s="158" t="str">
+      <c r="U160" s="234" t="str">
         <f>IF(B160="","",IFERROR(VLOOKUP(B160,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V160" s="159"/>
+      <c r="V160" s="235"/>
       <c r="W160" s="73"/>
       <c r="X160" s="88"/>
       <c r="Y160" s="97"/>
@@ -19387,15 +19439,15 @@
       <c r="A161" s="97"/>
       <c r="B161" s="92"/>
       <c r="C161" s="109"/>
-      <c r="D161" s="149" t="str">
+      <c r="D161" s="238" t="str">
         <f>IF(B161="","",IFERROR(VLOOKUP(B161,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E161" s="150"/>
-      <c r="F161" s="150"/>
-      <c r="G161" s="150"/>
-      <c r="H161" s="150"/>
-      <c r="I161" s="151"/>
+      <c r="E161" s="239"/>
+      <c r="F161" s="239"/>
+      <c r="G161" s="239"/>
+      <c r="H161" s="239"/>
+      <c r="I161" s="240"/>
       <c r="J161" s="104"/>
       <c r="K161" s="140" t="str">
         <f>IF(B161="","",IFERROR(VLOOKUP(B161,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -19422,11 +19474,11 @@
         <v/>
       </c>
       <c r="T161" s="99"/>
-      <c r="U161" s="158" t="str">
+      <c r="U161" s="234" t="str">
         <f>IF(B161="","",IFERROR(VLOOKUP(B161,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V161" s="159"/>
+      <c r="V161" s="235"/>
       <c r="W161" s="73"/>
       <c r="X161" s="88"/>
       <c r="Y161" s="97"/>
@@ -19435,15 +19487,15 @@
       <c r="A162" s="97"/>
       <c r="B162" s="89"/>
       <c r="C162" s="108"/>
-      <c r="D162" s="152" t="str">
+      <c r="D162" s="241" t="str">
         <f>IF(B162="","",IFERROR(VLOOKUP(B162,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E162" s="153"/>
-      <c r="F162" s="153"/>
-      <c r="G162" s="153"/>
-      <c r="H162" s="153"/>
-      <c r="I162" s="154"/>
+      <c r="E162" s="242"/>
+      <c r="F162" s="242"/>
+      <c r="G162" s="242"/>
+      <c r="H162" s="242"/>
+      <c r="I162" s="243"/>
       <c r="J162" s="103"/>
       <c r="K162" s="138" t="str">
         <f>IF(B162="","",IFERROR(VLOOKUP(B162,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -19470,11 +19522,11 @@
         <v/>
       </c>
       <c r="T162" s="96"/>
-      <c r="U162" s="158" t="str">
+      <c r="U162" s="234" t="str">
         <f>IF(B162="","",IFERROR(VLOOKUP(B162,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V162" s="159"/>
+      <c r="V162" s="235"/>
       <c r="W162" s="73"/>
       <c r="X162" s="88"/>
       <c r="Y162" s="97"/>
@@ -19483,15 +19535,15 @@
       <c r="A163" s="97"/>
       <c r="B163" s="92"/>
       <c r="C163" s="109"/>
-      <c r="D163" s="149" t="str">
+      <c r="D163" s="238" t="str">
         <f>IF(B163="","",IFERROR(VLOOKUP(B163,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E163" s="150"/>
-      <c r="F163" s="150"/>
-      <c r="G163" s="150"/>
-      <c r="H163" s="150"/>
-      <c r="I163" s="151"/>
+      <c r="E163" s="239"/>
+      <c r="F163" s="239"/>
+      <c r="G163" s="239"/>
+      <c r="H163" s="239"/>
+      <c r="I163" s="240"/>
       <c r="J163" s="104"/>
       <c r="K163" s="140" t="str">
         <f>IF(B163="","",IFERROR(VLOOKUP(B163,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -19518,11 +19570,11 @@
         <v/>
       </c>
       <c r="T163" s="99"/>
-      <c r="U163" s="158" t="str">
+      <c r="U163" s="234" t="str">
         <f>IF(B163="","",IFERROR(VLOOKUP(B163,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V163" s="159"/>
+      <c r="V163" s="235"/>
       <c r="W163" s="73"/>
       <c r="X163" s="88"/>
       <c r="Y163" s="97"/>
@@ -19531,15 +19583,15 @@
       <c r="A164" s="97"/>
       <c r="B164" s="89"/>
       <c r="C164" s="108"/>
-      <c r="D164" s="152" t="str">
+      <c r="D164" s="241" t="str">
         <f>IF(B164="","",IFERROR(VLOOKUP(B164,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E164" s="153"/>
-      <c r="F164" s="153"/>
-      <c r="G164" s="153"/>
-      <c r="H164" s="153"/>
-      <c r="I164" s="154"/>
+      <c r="E164" s="242"/>
+      <c r="F164" s="242"/>
+      <c r="G164" s="242"/>
+      <c r="H164" s="242"/>
+      <c r="I164" s="243"/>
       <c r="J164" s="103"/>
       <c r="K164" s="138" t="str">
         <f>IF(B164="","",IFERROR(VLOOKUP(B164,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -19566,11 +19618,11 @@
         <v/>
       </c>
       <c r="T164" s="96"/>
-      <c r="U164" s="158" t="str">
+      <c r="U164" s="234" t="str">
         <f>IF(B164="","",IFERROR(VLOOKUP(B164,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V164" s="159"/>
+      <c r="V164" s="235"/>
       <c r="W164" s="73"/>
       <c r="X164" s="88"/>
       <c r="Y164" s="97"/>
@@ -19579,15 +19631,15 @@
       <c r="A165" s="97"/>
       <c r="B165" s="92"/>
       <c r="C165" s="109"/>
-      <c r="D165" s="149" t="str">
+      <c r="D165" s="238" t="str">
         <f>IF(B165="","",IFERROR(VLOOKUP(B165,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E165" s="150"/>
-      <c r="F165" s="150"/>
-      <c r="G165" s="150"/>
-      <c r="H165" s="150"/>
-      <c r="I165" s="151"/>
+      <c r="E165" s="239"/>
+      <c r="F165" s="239"/>
+      <c r="G165" s="239"/>
+      <c r="H165" s="239"/>
+      <c r="I165" s="240"/>
       <c r="J165" s="104"/>
       <c r="K165" s="140" t="str">
         <f>IF(B165="","",IFERROR(VLOOKUP(B165,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -19614,11 +19666,11 @@
         <v/>
       </c>
       <c r="T165" s="99"/>
-      <c r="U165" s="158" t="str">
+      <c r="U165" s="234" t="str">
         <f>IF(B165="","",IFERROR(VLOOKUP(B165,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V165" s="159"/>
+      <c r="V165" s="235"/>
       <c r="W165" s="73"/>
       <c r="X165" s="88"/>
       <c r="Y165" s="97"/>
@@ -19627,15 +19679,15 @@
       <c r="A166" s="97"/>
       <c r="B166" s="89"/>
       <c r="C166" s="108"/>
-      <c r="D166" s="152" t="str">
+      <c r="D166" s="241" t="str">
         <f>IF(B166="","",IFERROR(VLOOKUP(B166,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E166" s="153"/>
-      <c r="F166" s="153"/>
-      <c r="G166" s="153"/>
-      <c r="H166" s="153"/>
-      <c r="I166" s="154"/>
+      <c r="E166" s="242"/>
+      <c r="F166" s="242"/>
+      <c r="G166" s="242"/>
+      <c r="H166" s="242"/>
+      <c r="I166" s="243"/>
       <c r="J166" s="103"/>
       <c r="K166" s="138" t="str">
         <f>IF(B166="","",IFERROR(VLOOKUP(B166,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -19662,11 +19714,11 @@
         <v/>
       </c>
       <c r="T166" s="96"/>
-      <c r="U166" s="158" t="str">
+      <c r="U166" s="234" t="str">
         <f>IF(B166="","",IFERROR(VLOOKUP(B166,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V166" s="159"/>
+      <c r="V166" s="235"/>
       <c r="W166" s="73"/>
       <c r="X166" s="88"/>
       <c r="Y166" s="97"/>
@@ -19675,15 +19727,15 @@
       <c r="A167" s="97"/>
       <c r="B167" s="92"/>
       <c r="C167" s="109"/>
-      <c r="D167" s="149" t="str">
+      <c r="D167" s="238" t="str">
         <f>IF(B167="","",IFERROR(VLOOKUP(B167,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E167" s="150"/>
-      <c r="F167" s="150"/>
-      <c r="G167" s="150"/>
-      <c r="H167" s="150"/>
-      <c r="I167" s="151"/>
+      <c r="E167" s="239"/>
+      <c r="F167" s="239"/>
+      <c r="G167" s="239"/>
+      <c r="H167" s="239"/>
+      <c r="I167" s="240"/>
       <c r="J167" s="104"/>
       <c r="K167" s="140" t="str">
         <f>IF(B167="","",IFERROR(VLOOKUP(B167,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -19710,11 +19762,11 @@
         <v/>
       </c>
       <c r="T167" s="99"/>
-      <c r="U167" s="158" t="str">
+      <c r="U167" s="234" t="str">
         <f>IF(B167="","",IFERROR(VLOOKUP(B167,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V167" s="159"/>
+      <c r="V167" s="235"/>
       <c r="W167" s="73"/>
       <c r="X167" s="88"/>
       <c r="Y167" s="97"/>
@@ -19723,15 +19775,15 @@
       <c r="A168" s="97"/>
       <c r="B168" s="89"/>
       <c r="C168" s="108"/>
-      <c r="D168" s="152" t="str">
+      <c r="D168" s="241" t="str">
         <f>IF(B168="","",IFERROR(VLOOKUP(B168,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E168" s="153"/>
-      <c r="F168" s="153"/>
-      <c r="G168" s="153"/>
-      <c r="H168" s="153"/>
-      <c r="I168" s="154"/>
+      <c r="E168" s="242"/>
+      <c r="F168" s="242"/>
+      <c r="G168" s="242"/>
+      <c r="H168" s="242"/>
+      <c r="I168" s="243"/>
       <c r="J168" s="103"/>
       <c r="K168" s="138" t="str">
         <f>IF(B168="","",IFERROR(VLOOKUP(B168,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -19758,11 +19810,11 @@
         <v/>
       </c>
       <c r="T168" s="96"/>
-      <c r="U168" s="158" t="str">
+      <c r="U168" s="234" t="str">
         <f>IF(B168="","",IFERROR(VLOOKUP(B168,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V168" s="159"/>
+      <c r="V168" s="235"/>
       <c r="W168" s="73"/>
       <c r="X168" s="88"/>
       <c r="Y168" s="97"/>
@@ -19771,15 +19823,15 @@
       <c r="A169" s="97"/>
       <c r="B169" s="92"/>
       <c r="C169" s="109"/>
-      <c r="D169" s="149" t="str">
+      <c r="D169" s="238" t="str">
         <f>IF(B169="","",IFERROR(VLOOKUP(B169,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E169" s="150"/>
-      <c r="F169" s="150"/>
-      <c r="G169" s="150"/>
-      <c r="H169" s="150"/>
-      <c r="I169" s="151"/>
+      <c r="E169" s="239"/>
+      <c r="F169" s="239"/>
+      <c r="G169" s="239"/>
+      <c r="H169" s="239"/>
+      <c r="I169" s="240"/>
       <c r="J169" s="104"/>
       <c r="K169" s="140" t="str">
         <f>IF(B169="","",IFERROR(VLOOKUP(B169,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -19806,11 +19858,11 @@
         <v/>
       </c>
       <c r="T169" s="99"/>
-      <c r="U169" s="158" t="str">
+      <c r="U169" s="234" t="str">
         <f>IF(B169="","",IFERROR(VLOOKUP(B169,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V169" s="159"/>
+      <c r="V169" s="235"/>
       <c r="W169" s="73"/>
       <c r="X169" s="88"/>
       <c r="Y169" s="97"/>
@@ -19819,15 +19871,15 @@
       <c r="A170" s="97"/>
       <c r="B170" s="89"/>
       <c r="C170" s="108"/>
-      <c r="D170" s="152" t="str">
+      <c r="D170" s="241" t="str">
         <f>IF(B170="","",IFERROR(VLOOKUP(B170,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E170" s="153"/>
-      <c r="F170" s="153"/>
-      <c r="G170" s="153"/>
-      <c r="H170" s="153"/>
-      <c r="I170" s="154"/>
+      <c r="E170" s="242"/>
+      <c r="F170" s="242"/>
+      <c r="G170" s="242"/>
+      <c r="H170" s="242"/>
+      <c r="I170" s="243"/>
       <c r="J170" s="103"/>
       <c r="K170" s="138" t="str">
         <f>IF(B170="","",IFERROR(VLOOKUP(B170,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -19854,11 +19906,11 @@
         <v/>
       </c>
       <c r="T170" s="96"/>
-      <c r="U170" s="158" t="str">
+      <c r="U170" s="234" t="str">
         <f>IF(B170="","",IFERROR(VLOOKUP(B170,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V170" s="159"/>
+      <c r="V170" s="235"/>
       <c r="W170" s="73"/>
       <c r="X170" s="88"/>
       <c r="Y170" s="97"/>
@@ -19867,15 +19919,15 @@
       <c r="A171" s="97"/>
       <c r="B171" s="92"/>
       <c r="C171" s="109"/>
-      <c r="D171" s="149" t="str">
+      <c r="D171" s="238" t="str">
         <f>IF(B171="","",IFERROR(VLOOKUP(B171,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E171" s="150"/>
-      <c r="F171" s="150"/>
-      <c r="G171" s="150"/>
-      <c r="H171" s="150"/>
-      <c r="I171" s="151"/>
+      <c r="E171" s="239"/>
+      <c r="F171" s="239"/>
+      <c r="G171" s="239"/>
+      <c r="H171" s="239"/>
+      <c r="I171" s="240"/>
       <c r="J171" s="104"/>
       <c r="K171" s="140" t="str">
         <f>IF(B171="","",IFERROR(VLOOKUP(B171,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -19902,11 +19954,11 @@
         <v/>
       </c>
       <c r="T171" s="99"/>
-      <c r="U171" s="158" t="str">
+      <c r="U171" s="234" t="str">
         <f>IF(B171="","",IFERROR(VLOOKUP(B171,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V171" s="159"/>
+      <c r="V171" s="235"/>
       <c r="W171" s="73"/>
       <c r="X171" s="88"/>
       <c r="Y171" s="97"/>
@@ -19915,15 +19967,15 @@
       <c r="A172" s="97"/>
       <c r="B172" s="89"/>
       <c r="C172" s="108"/>
-      <c r="D172" s="152" t="str">
+      <c r="D172" s="241" t="str">
         <f>IF(B172="","",IFERROR(VLOOKUP(B172,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E172" s="153"/>
-      <c r="F172" s="153"/>
-      <c r="G172" s="153"/>
-      <c r="H172" s="153"/>
-      <c r="I172" s="154"/>
+      <c r="E172" s="242"/>
+      <c r="F172" s="242"/>
+      <c r="G172" s="242"/>
+      <c r="H172" s="242"/>
+      <c r="I172" s="243"/>
       <c r="J172" s="103"/>
       <c r="K172" s="138" t="str">
         <f>IF(B172="","",IFERROR(VLOOKUP(B172,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -19950,11 +20002,11 @@
         <v/>
       </c>
       <c r="T172" s="96"/>
-      <c r="U172" s="158" t="str">
+      <c r="U172" s="234" t="str">
         <f>IF(B172="","",IFERROR(VLOOKUP(B172,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V172" s="159"/>
+      <c r="V172" s="235"/>
       <c r="W172" s="73"/>
       <c r="X172" s="88"/>
       <c r="Y172" s="97"/>
@@ -19963,15 +20015,15 @@
       <c r="A173" s="97"/>
       <c r="B173" s="92"/>
       <c r="C173" s="109"/>
-      <c r="D173" s="149" t="str">
+      <c r="D173" s="238" t="str">
         <f>IF(B173="","",IFERROR(VLOOKUP(B173,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E173" s="150"/>
-      <c r="F173" s="150"/>
-      <c r="G173" s="150"/>
-      <c r="H173" s="150"/>
-      <c r="I173" s="151"/>
+      <c r="E173" s="239"/>
+      <c r="F173" s="239"/>
+      <c r="G173" s="239"/>
+      <c r="H173" s="239"/>
+      <c r="I173" s="240"/>
       <c r="J173" s="104"/>
       <c r="K173" s="140" t="str">
         <f>IF(B173="","",IFERROR(VLOOKUP(B173,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -19998,11 +20050,11 @@
         <v/>
       </c>
       <c r="T173" s="99"/>
-      <c r="U173" s="158" t="str">
+      <c r="U173" s="234" t="str">
         <f>IF(B173="","",IFERROR(VLOOKUP(B173,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V173" s="159"/>
+      <c r="V173" s="235"/>
       <c r="W173" s="73"/>
       <c r="X173" s="88"/>
       <c r="Y173" s="97"/>
@@ -20011,15 +20063,15 @@
       <c r="A174" s="97"/>
       <c r="B174" s="89"/>
       <c r="C174" s="108"/>
-      <c r="D174" s="152" t="str">
+      <c r="D174" s="241" t="str">
         <f>IF(B174="","",IFERROR(VLOOKUP(B174,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E174" s="153"/>
-      <c r="F174" s="153"/>
-      <c r="G174" s="153"/>
-      <c r="H174" s="153"/>
-      <c r="I174" s="154"/>
+      <c r="E174" s="242"/>
+      <c r="F174" s="242"/>
+      <c r="G174" s="242"/>
+      <c r="H174" s="242"/>
+      <c r="I174" s="243"/>
       <c r="J174" s="103"/>
       <c r="K174" s="138" t="str">
         <f>IF(B174="","",IFERROR(VLOOKUP(B174,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -20046,11 +20098,11 @@
         <v/>
       </c>
       <c r="T174" s="96"/>
-      <c r="U174" s="158" t="str">
+      <c r="U174" s="234" t="str">
         <f>IF(B174="","",IFERROR(VLOOKUP(B174,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V174" s="159"/>
+      <c r="V174" s="235"/>
       <c r="W174" s="73"/>
       <c r="X174" s="88"/>
       <c r="Y174" s="97"/>
@@ -20059,15 +20111,15 @@
       <c r="A175" s="97"/>
       <c r="B175" s="92"/>
       <c r="C175" s="109"/>
-      <c r="D175" s="149" t="str">
+      <c r="D175" s="238" t="str">
         <f>IF(B175="","",IFERROR(VLOOKUP(B175,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E175" s="150"/>
-      <c r="F175" s="150"/>
-      <c r="G175" s="150"/>
-      <c r="H175" s="150"/>
-      <c r="I175" s="151"/>
+      <c r="E175" s="239"/>
+      <c r="F175" s="239"/>
+      <c r="G175" s="239"/>
+      <c r="H175" s="239"/>
+      <c r="I175" s="240"/>
       <c r="J175" s="104"/>
       <c r="K175" s="140" t="str">
         <f>IF(B175="","",IFERROR(VLOOKUP(B175,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -20094,11 +20146,11 @@
         <v/>
       </c>
       <c r="T175" s="99"/>
-      <c r="U175" s="158" t="str">
+      <c r="U175" s="234" t="str">
         <f>IF(B175="","",IFERROR(VLOOKUP(B175,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V175" s="159"/>
+      <c r="V175" s="235"/>
       <c r="W175" s="73"/>
       <c r="X175" s="88"/>
       <c r="Y175" s="97"/>
@@ -20107,15 +20159,15 @@
       <c r="A176" s="97"/>
       <c r="B176" s="89"/>
       <c r="C176" s="108"/>
-      <c r="D176" s="152" t="str">
+      <c r="D176" s="241" t="str">
         <f>IF(B176="","",IFERROR(VLOOKUP(B176,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E176" s="153"/>
-      <c r="F176" s="153"/>
-      <c r="G176" s="153"/>
-      <c r="H176" s="153"/>
-      <c r="I176" s="154"/>
+      <c r="E176" s="242"/>
+      <c r="F176" s="242"/>
+      <c r="G176" s="242"/>
+      <c r="H176" s="242"/>
+      <c r="I176" s="243"/>
       <c r="J176" s="103"/>
       <c r="K176" s="138" t="str">
         <f>IF(B176="","",IFERROR(VLOOKUP(B176,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -20142,11 +20194,11 @@
         <v/>
       </c>
       <c r="T176" s="96"/>
-      <c r="U176" s="158" t="str">
+      <c r="U176" s="234" t="str">
         <f>IF(B176="","",IFERROR(VLOOKUP(B176,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V176" s="159"/>
+      <c r="V176" s="235"/>
       <c r="W176" s="73"/>
       <c r="X176" s="88"/>
       <c r="Y176" s="97"/>
@@ -20155,15 +20207,15 @@
       <c r="A177" s="97"/>
       <c r="B177" s="92"/>
       <c r="C177" s="109"/>
-      <c r="D177" s="149" t="str">
+      <c r="D177" s="238" t="str">
         <f>IF(B177="","",IFERROR(VLOOKUP(B177,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E177" s="150"/>
-      <c r="F177" s="150"/>
-      <c r="G177" s="150"/>
-      <c r="H177" s="150"/>
-      <c r="I177" s="151"/>
+      <c r="E177" s="239"/>
+      <c r="F177" s="239"/>
+      <c r="G177" s="239"/>
+      <c r="H177" s="239"/>
+      <c r="I177" s="240"/>
       <c r="J177" s="104"/>
       <c r="K177" s="140" t="str">
         <f>IF(B177="","",IFERROR(VLOOKUP(B177,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -20190,11 +20242,11 @@
         <v/>
       </c>
       <c r="T177" s="99"/>
-      <c r="U177" s="158" t="str">
+      <c r="U177" s="234" t="str">
         <f>IF(B177="","",IFERROR(VLOOKUP(B177,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V177" s="159"/>
+      <c r="V177" s="235"/>
       <c r="W177" s="73"/>
       <c r="X177" s="88"/>
       <c r="Y177" s="97"/>
@@ -20203,15 +20255,15 @@
       <c r="A178" s="97"/>
       <c r="B178" s="89"/>
       <c r="C178" s="108"/>
-      <c r="D178" s="152" t="str">
+      <c r="D178" s="241" t="str">
         <f>IF(B178="","",IFERROR(VLOOKUP(B178,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E178" s="153"/>
-      <c r="F178" s="153"/>
-      <c r="G178" s="153"/>
-      <c r="H178" s="153"/>
-      <c r="I178" s="154"/>
+      <c r="E178" s="242"/>
+      <c r="F178" s="242"/>
+      <c r="G178" s="242"/>
+      <c r="H178" s="242"/>
+      <c r="I178" s="243"/>
       <c r="J178" s="103"/>
       <c r="K178" s="138" t="str">
         <f>IF(B178="","",IFERROR(VLOOKUP(B178,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -20238,11 +20290,11 @@
         <v/>
       </c>
       <c r="T178" s="96"/>
-      <c r="U178" s="158" t="str">
+      <c r="U178" s="234" t="str">
         <f>IF(B178="","",IFERROR(VLOOKUP(B178,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V178" s="159"/>
+      <c r="V178" s="235"/>
       <c r="W178" s="73"/>
       <c r="X178" s="88"/>
       <c r="Y178" s="97"/>
@@ -20251,15 +20303,15 @@
       <c r="A179" s="97"/>
       <c r="B179" s="92"/>
       <c r="C179" s="109"/>
-      <c r="D179" s="149" t="str">
+      <c r="D179" s="238" t="str">
         <f>IF(B179="","",IFERROR(VLOOKUP(B179,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E179" s="150"/>
-      <c r="F179" s="150"/>
-      <c r="G179" s="150"/>
-      <c r="H179" s="150"/>
-      <c r="I179" s="151"/>
+      <c r="E179" s="239"/>
+      <c r="F179" s="239"/>
+      <c r="G179" s="239"/>
+      <c r="H179" s="239"/>
+      <c r="I179" s="240"/>
       <c r="J179" s="104"/>
       <c r="K179" s="140" t="str">
         <f>IF(B179="","",IFERROR(VLOOKUP(B179,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -20286,11 +20338,11 @@
         <v/>
       </c>
       <c r="T179" s="99"/>
-      <c r="U179" s="158" t="str">
+      <c r="U179" s="234" t="str">
         <f>IF(B179="","",IFERROR(VLOOKUP(B179,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V179" s="159"/>
+      <c r="V179" s="235"/>
       <c r="W179" s="73"/>
       <c r="X179" s="88"/>
       <c r="Y179" s="97"/>
@@ -20299,15 +20351,15 @@
       <c r="A180" s="97"/>
       <c r="B180" s="89"/>
       <c r="C180" s="108"/>
-      <c r="D180" s="152" t="str">
+      <c r="D180" s="241" t="str">
         <f>IF(B180="","",IFERROR(VLOOKUP(B180,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E180" s="153"/>
-      <c r="F180" s="153"/>
-      <c r="G180" s="153"/>
-      <c r="H180" s="153"/>
-      <c r="I180" s="154"/>
+      <c r="E180" s="242"/>
+      <c r="F180" s="242"/>
+      <c r="G180" s="242"/>
+      <c r="H180" s="242"/>
+      <c r="I180" s="243"/>
       <c r="J180" s="103"/>
       <c r="K180" s="138" t="str">
         <f>IF(B180="","",IFERROR(VLOOKUP(B180,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -20334,11 +20386,11 @@
         <v/>
       </c>
       <c r="T180" s="96"/>
-      <c r="U180" s="158" t="str">
+      <c r="U180" s="234" t="str">
         <f>IF(B180="","",IFERROR(VLOOKUP(B180,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V180" s="159"/>
+      <c r="V180" s="235"/>
       <c r="W180" s="73"/>
       <c r="X180" s="88"/>
       <c r="Y180" s="97"/>
@@ -20347,15 +20399,15 @@
       <c r="A181" s="97"/>
       <c r="B181" s="92"/>
       <c r="C181" s="109"/>
-      <c r="D181" s="149" t="str">
+      <c r="D181" s="238" t="str">
         <f>IF(B181="","",IFERROR(VLOOKUP(B181,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E181" s="150"/>
-      <c r="F181" s="150"/>
-      <c r="G181" s="150"/>
-      <c r="H181" s="150"/>
-      <c r="I181" s="151"/>
+      <c r="E181" s="239"/>
+      <c r="F181" s="239"/>
+      <c r="G181" s="239"/>
+      <c r="H181" s="239"/>
+      <c r="I181" s="240"/>
       <c r="J181" s="104"/>
       <c r="K181" s="140" t="str">
         <f>IF(B181="","",IFERROR(VLOOKUP(B181,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -20382,11 +20434,11 @@
         <v/>
       </c>
       <c r="T181" s="99"/>
-      <c r="U181" s="158" t="str">
+      <c r="U181" s="234" t="str">
         <f>IF(B181="","",IFERROR(VLOOKUP(B181,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V181" s="159"/>
+      <c r="V181" s="235"/>
       <c r="W181" s="73"/>
       <c r="X181" s="88"/>
       <c r="Y181" s="97"/>
@@ -20395,15 +20447,15 @@
       <c r="A182" s="97"/>
       <c r="B182" s="89"/>
       <c r="C182" s="108"/>
-      <c r="D182" s="152" t="str">
+      <c r="D182" s="241" t="str">
         <f>IF(B182="","",IFERROR(VLOOKUP(B182,'Bug Tracker'!$A:$L,2,FALSE),"Not Found"))</f>
         <v/>
       </c>
-      <c r="E182" s="153"/>
-      <c r="F182" s="153"/>
-      <c r="G182" s="153"/>
-      <c r="H182" s="153"/>
-      <c r="I182" s="154"/>
+      <c r="E182" s="242"/>
+      <c r="F182" s="242"/>
+      <c r="G182" s="242"/>
+      <c r="H182" s="242"/>
+      <c r="I182" s="243"/>
       <c r="J182" s="103"/>
       <c r="K182" s="138" t="str">
         <f>IF(B182="","",IFERROR(VLOOKUP(B182,'Bug Tracker'!$A:$L,3,FALSE),""))</f>
@@ -20430,11 +20482,11 @@
         <v/>
       </c>
       <c r="T182" s="96"/>
-      <c r="U182" s="158" t="str">
+      <c r="U182" s="234" t="str">
         <f>IF(B182="","",IFERROR(VLOOKUP(B182,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V182" s="159"/>
+      <c r="V182" s="235"/>
       <c r="W182" s="73"/>
       <c r="X182" s="88"/>
       <c r="Y182" s="97"/>
@@ -20443,12 +20495,12 @@
       <c r="A183" s="97"/>
       <c r="B183" s="100"/>
       <c r="C183" s="110"/>
-      <c r="D183" s="155"/>
-      <c r="E183" s="156"/>
-      <c r="F183" s="156"/>
-      <c r="G183" s="156"/>
-      <c r="H183" s="156"/>
-      <c r="I183" s="157"/>
+      <c r="D183" s="244"/>
+      <c r="E183" s="245"/>
+      <c r="F183" s="245"/>
+      <c r="G183" s="245"/>
+      <c r="H183" s="245"/>
+      <c r="I183" s="246"/>
       <c r="J183" s="105"/>
       <c r="K183" s="142"/>
       <c r="L183" s="101"/>
@@ -20460,57 +20512,198 @@
       <c r="R183" s="101"/>
       <c r="S183" s="143"/>
       <c r="T183" s="102"/>
-      <c r="U183" s="160" t="str">
+      <c r="U183" s="236" t="str">
         <f>IF(B183="","",IFERROR(VLOOKUP(B183,'Bug Tracker'!$A:$L,10,FALSE),""))</f>
         <v/>
       </c>
-      <c r="V183" s="161"/>
+      <c r="V183" s="237"/>
       <c r="W183" s="73"/>
       <c r="X183" s="88"/>
       <c r="Y183" s="97"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="244">
-    <mergeCell ref="U89:V89"/>
-    <mergeCell ref="K83"/>
-    <mergeCell ref="U83:V83"/>
-    <mergeCell ref="V8:X8"/>
-    <mergeCell ref="B29:K29"/>
-    <mergeCell ref="J9:L9"/>
-    <mergeCell ref="L29:X29"/>
-    <mergeCell ref="U84:V84"/>
-    <mergeCell ref="R9:T9"/>
-    <mergeCell ref="U87:V87"/>
-    <mergeCell ref="J8:L8"/>
-    <mergeCell ref="R8:T8"/>
-    <mergeCell ref="B48:K48"/>
-    <mergeCell ref="Q83"/>
-    <mergeCell ref="B11:K11"/>
-    <mergeCell ref="B83"/>
-    <mergeCell ref="D86:I86"/>
-    <mergeCell ref="D85:I85"/>
-    <mergeCell ref="B2:X2"/>
-    <mergeCell ref="M83"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="V7:X7"/>
-    <mergeCell ref="N6:P6"/>
-    <mergeCell ref="D83:I83"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="R7:T7"/>
-    <mergeCell ref="R6:T6"/>
-    <mergeCell ref="B4:X4"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B65:K65"/>
-    <mergeCell ref="L65:X65"/>
-    <mergeCell ref="V9:X9"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="O83"/>
-    <mergeCell ref="S83"/>
-    <mergeCell ref="B3:X3"/>
+    <mergeCell ref="D179:I179"/>
+    <mergeCell ref="D180:I180"/>
+    <mergeCell ref="D181:I181"/>
+    <mergeCell ref="D182:I182"/>
+    <mergeCell ref="D183:I183"/>
+    <mergeCell ref="D174:I174"/>
+    <mergeCell ref="D175:I175"/>
+    <mergeCell ref="D176:I176"/>
+    <mergeCell ref="D177:I177"/>
+    <mergeCell ref="D178:I178"/>
+    <mergeCell ref="D169:I169"/>
+    <mergeCell ref="D170:I170"/>
+    <mergeCell ref="D171:I171"/>
+    <mergeCell ref="D172:I172"/>
+    <mergeCell ref="D173:I173"/>
+    <mergeCell ref="D164:I164"/>
+    <mergeCell ref="D165:I165"/>
+    <mergeCell ref="D166:I166"/>
+    <mergeCell ref="D167:I167"/>
+    <mergeCell ref="D168:I168"/>
+    <mergeCell ref="D159:I159"/>
+    <mergeCell ref="D160:I160"/>
+    <mergeCell ref="D161:I161"/>
+    <mergeCell ref="D162:I162"/>
+    <mergeCell ref="D163:I163"/>
+    <mergeCell ref="D154:I154"/>
+    <mergeCell ref="D155:I155"/>
+    <mergeCell ref="D156:I156"/>
+    <mergeCell ref="D157:I157"/>
+    <mergeCell ref="D158:I158"/>
+    <mergeCell ref="D149:I149"/>
+    <mergeCell ref="D150:I150"/>
+    <mergeCell ref="D151:I151"/>
+    <mergeCell ref="D152:I152"/>
+    <mergeCell ref="D153:I153"/>
+    <mergeCell ref="D144:I144"/>
+    <mergeCell ref="D145:I145"/>
+    <mergeCell ref="D146:I146"/>
+    <mergeCell ref="D147:I147"/>
+    <mergeCell ref="D148:I148"/>
+    <mergeCell ref="D139:I139"/>
+    <mergeCell ref="D140:I140"/>
+    <mergeCell ref="D141:I141"/>
+    <mergeCell ref="D142:I142"/>
+    <mergeCell ref="D143:I143"/>
+    <mergeCell ref="D134:I134"/>
+    <mergeCell ref="D135:I135"/>
+    <mergeCell ref="D136:I136"/>
+    <mergeCell ref="D137:I137"/>
+    <mergeCell ref="D138:I138"/>
+    <mergeCell ref="D129:I129"/>
+    <mergeCell ref="D130:I130"/>
+    <mergeCell ref="D131:I131"/>
+    <mergeCell ref="D132:I132"/>
+    <mergeCell ref="D133:I133"/>
+    <mergeCell ref="D124:I124"/>
+    <mergeCell ref="D125:I125"/>
+    <mergeCell ref="D126:I126"/>
+    <mergeCell ref="D127:I127"/>
+    <mergeCell ref="D128:I128"/>
+    <mergeCell ref="D119:I119"/>
+    <mergeCell ref="D120:I120"/>
+    <mergeCell ref="D121:I121"/>
+    <mergeCell ref="D122:I122"/>
+    <mergeCell ref="D123:I123"/>
+    <mergeCell ref="D114:I114"/>
+    <mergeCell ref="D115:I115"/>
+    <mergeCell ref="D116:I116"/>
+    <mergeCell ref="D117:I117"/>
+    <mergeCell ref="D118:I118"/>
+    <mergeCell ref="D109:I109"/>
+    <mergeCell ref="D110:I110"/>
+    <mergeCell ref="D111:I111"/>
+    <mergeCell ref="D112:I112"/>
+    <mergeCell ref="D113:I113"/>
+    <mergeCell ref="D104:I104"/>
+    <mergeCell ref="D105:I105"/>
+    <mergeCell ref="D106:I106"/>
+    <mergeCell ref="D107:I107"/>
+    <mergeCell ref="D108:I108"/>
+    <mergeCell ref="D99:I99"/>
+    <mergeCell ref="D100:I100"/>
+    <mergeCell ref="D101:I101"/>
+    <mergeCell ref="D102:I102"/>
+    <mergeCell ref="D103:I103"/>
+    <mergeCell ref="D94:I94"/>
+    <mergeCell ref="D95:I95"/>
+    <mergeCell ref="D96:I96"/>
+    <mergeCell ref="D97:I97"/>
+    <mergeCell ref="D98:I98"/>
+    <mergeCell ref="U179:V179"/>
+    <mergeCell ref="U180:V180"/>
+    <mergeCell ref="U181:V181"/>
+    <mergeCell ref="U182:V182"/>
+    <mergeCell ref="U183:V183"/>
+    <mergeCell ref="U174:V174"/>
+    <mergeCell ref="U175:V175"/>
+    <mergeCell ref="U176:V176"/>
+    <mergeCell ref="U177:V177"/>
+    <mergeCell ref="U178:V178"/>
+    <mergeCell ref="U169:V169"/>
+    <mergeCell ref="U170:V170"/>
+    <mergeCell ref="U171:V171"/>
+    <mergeCell ref="U172:V172"/>
+    <mergeCell ref="U173:V173"/>
+    <mergeCell ref="U164:V164"/>
+    <mergeCell ref="U165:V165"/>
+    <mergeCell ref="U166:V166"/>
+    <mergeCell ref="U167:V167"/>
+    <mergeCell ref="U168:V168"/>
+    <mergeCell ref="U159:V159"/>
+    <mergeCell ref="U160:V160"/>
+    <mergeCell ref="U161:V161"/>
+    <mergeCell ref="U162:V162"/>
+    <mergeCell ref="U163:V163"/>
+    <mergeCell ref="U154:V154"/>
+    <mergeCell ref="U155:V155"/>
+    <mergeCell ref="U156:V156"/>
+    <mergeCell ref="U157:V157"/>
+    <mergeCell ref="U158:V158"/>
+    <mergeCell ref="U149:V149"/>
+    <mergeCell ref="U150:V150"/>
+    <mergeCell ref="U151:V151"/>
+    <mergeCell ref="U152:V152"/>
+    <mergeCell ref="U153:V153"/>
+    <mergeCell ref="U144:V144"/>
+    <mergeCell ref="U145:V145"/>
+    <mergeCell ref="U146:V146"/>
+    <mergeCell ref="U147:V147"/>
+    <mergeCell ref="U148:V148"/>
+    <mergeCell ref="U139:V139"/>
+    <mergeCell ref="U140:V140"/>
+    <mergeCell ref="U141:V141"/>
+    <mergeCell ref="U142:V142"/>
+    <mergeCell ref="U143:V143"/>
+    <mergeCell ref="U134:V134"/>
+    <mergeCell ref="U135:V135"/>
+    <mergeCell ref="U136:V136"/>
+    <mergeCell ref="U137:V137"/>
+    <mergeCell ref="U138:V138"/>
+    <mergeCell ref="U129:V129"/>
+    <mergeCell ref="U130:V130"/>
+    <mergeCell ref="U131:V131"/>
+    <mergeCell ref="U132:V132"/>
+    <mergeCell ref="U133:V133"/>
+    <mergeCell ref="U124:V124"/>
+    <mergeCell ref="U125:V125"/>
+    <mergeCell ref="U126:V126"/>
+    <mergeCell ref="U127:V127"/>
+    <mergeCell ref="U128:V128"/>
+    <mergeCell ref="U119:V119"/>
+    <mergeCell ref="U120:V120"/>
+    <mergeCell ref="U121:V121"/>
+    <mergeCell ref="U122:V122"/>
+    <mergeCell ref="U123:V123"/>
+    <mergeCell ref="U114:V114"/>
+    <mergeCell ref="U115:V115"/>
+    <mergeCell ref="U116:V116"/>
+    <mergeCell ref="U117:V117"/>
+    <mergeCell ref="U118:V118"/>
+    <mergeCell ref="U109:V109"/>
+    <mergeCell ref="U110:V110"/>
+    <mergeCell ref="U111:V111"/>
+    <mergeCell ref="U112:V112"/>
+    <mergeCell ref="U113:V113"/>
+    <mergeCell ref="U104:V104"/>
+    <mergeCell ref="U105:V105"/>
+    <mergeCell ref="U106:V106"/>
+    <mergeCell ref="U107:V107"/>
+    <mergeCell ref="U108:V108"/>
+    <mergeCell ref="U99:V99"/>
+    <mergeCell ref="U100:V100"/>
+    <mergeCell ref="U101:V101"/>
+    <mergeCell ref="U102:V102"/>
+    <mergeCell ref="U103:V103"/>
+    <mergeCell ref="U94:V94"/>
+    <mergeCell ref="U95:V95"/>
+    <mergeCell ref="U96:V96"/>
+    <mergeCell ref="U97:V97"/>
+    <mergeCell ref="U98:V98"/>
     <mergeCell ref="D93:I93"/>
     <mergeCell ref="J6:L6"/>
     <mergeCell ref="D92:I92"/>
@@ -20535,186 +20728,46 @@
     <mergeCell ref="N9:P9"/>
     <mergeCell ref="F9:H9"/>
     <mergeCell ref="U85:V85"/>
-    <mergeCell ref="U99:V99"/>
-    <mergeCell ref="U100:V100"/>
-    <mergeCell ref="U101:V101"/>
-    <mergeCell ref="U102:V102"/>
-    <mergeCell ref="U103:V103"/>
-    <mergeCell ref="U94:V94"/>
-    <mergeCell ref="U95:V95"/>
-    <mergeCell ref="U96:V96"/>
-    <mergeCell ref="U97:V97"/>
-    <mergeCell ref="U98:V98"/>
-    <mergeCell ref="U109:V109"/>
-    <mergeCell ref="U110:V110"/>
-    <mergeCell ref="U111:V111"/>
-    <mergeCell ref="U112:V112"/>
-    <mergeCell ref="U113:V113"/>
-    <mergeCell ref="U104:V104"/>
-    <mergeCell ref="U105:V105"/>
-    <mergeCell ref="U106:V106"/>
-    <mergeCell ref="U107:V107"/>
-    <mergeCell ref="U108:V108"/>
-    <mergeCell ref="U119:V119"/>
-    <mergeCell ref="U120:V120"/>
-    <mergeCell ref="U121:V121"/>
-    <mergeCell ref="U122:V122"/>
-    <mergeCell ref="U123:V123"/>
-    <mergeCell ref="U114:V114"/>
-    <mergeCell ref="U115:V115"/>
-    <mergeCell ref="U116:V116"/>
-    <mergeCell ref="U117:V117"/>
-    <mergeCell ref="U118:V118"/>
-    <mergeCell ref="U129:V129"/>
-    <mergeCell ref="U130:V130"/>
-    <mergeCell ref="U131:V131"/>
-    <mergeCell ref="U132:V132"/>
-    <mergeCell ref="U133:V133"/>
-    <mergeCell ref="U124:V124"/>
-    <mergeCell ref="U125:V125"/>
-    <mergeCell ref="U126:V126"/>
-    <mergeCell ref="U127:V127"/>
-    <mergeCell ref="U128:V128"/>
-    <mergeCell ref="U139:V139"/>
-    <mergeCell ref="U140:V140"/>
-    <mergeCell ref="U141:V141"/>
-    <mergeCell ref="U142:V142"/>
-    <mergeCell ref="U143:V143"/>
-    <mergeCell ref="U134:V134"/>
-    <mergeCell ref="U135:V135"/>
-    <mergeCell ref="U136:V136"/>
-    <mergeCell ref="U137:V137"/>
-    <mergeCell ref="U138:V138"/>
-    <mergeCell ref="U149:V149"/>
-    <mergeCell ref="U150:V150"/>
-    <mergeCell ref="U151:V151"/>
-    <mergeCell ref="U152:V152"/>
-    <mergeCell ref="U153:V153"/>
-    <mergeCell ref="U144:V144"/>
-    <mergeCell ref="U145:V145"/>
-    <mergeCell ref="U146:V146"/>
-    <mergeCell ref="U147:V147"/>
-    <mergeCell ref="U148:V148"/>
-    <mergeCell ref="U159:V159"/>
-    <mergeCell ref="U160:V160"/>
-    <mergeCell ref="U161:V161"/>
-    <mergeCell ref="U162:V162"/>
-    <mergeCell ref="U163:V163"/>
-    <mergeCell ref="U154:V154"/>
-    <mergeCell ref="U155:V155"/>
-    <mergeCell ref="U156:V156"/>
-    <mergeCell ref="U157:V157"/>
-    <mergeCell ref="U158:V158"/>
-    <mergeCell ref="U169:V169"/>
-    <mergeCell ref="U170:V170"/>
-    <mergeCell ref="U171:V171"/>
-    <mergeCell ref="U172:V172"/>
-    <mergeCell ref="U173:V173"/>
-    <mergeCell ref="U164:V164"/>
-    <mergeCell ref="U165:V165"/>
-    <mergeCell ref="U166:V166"/>
-    <mergeCell ref="U167:V167"/>
-    <mergeCell ref="U168:V168"/>
-    <mergeCell ref="U179:V179"/>
-    <mergeCell ref="U180:V180"/>
-    <mergeCell ref="U181:V181"/>
-    <mergeCell ref="U182:V182"/>
-    <mergeCell ref="U183:V183"/>
-    <mergeCell ref="U174:V174"/>
-    <mergeCell ref="U175:V175"/>
-    <mergeCell ref="U176:V176"/>
-    <mergeCell ref="U177:V177"/>
-    <mergeCell ref="U178:V178"/>
-    <mergeCell ref="D99:I99"/>
-    <mergeCell ref="D100:I100"/>
-    <mergeCell ref="D101:I101"/>
-    <mergeCell ref="D102:I102"/>
-    <mergeCell ref="D103:I103"/>
-    <mergeCell ref="D94:I94"/>
-    <mergeCell ref="D95:I95"/>
-    <mergeCell ref="D96:I96"/>
-    <mergeCell ref="D97:I97"/>
-    <mergeCell ref="D98:I98"/>
-    <mergeCell ref="D109:I109"/>
-    <mergeCell ref="D110:I110"/>
-    <mergeCell ref="D111:I111"/>
-    <mergeCell ref="D112:I112"/>
-    <mergeCell ref="D113:I113"/>
-    <mergeCell ref="D104:I104"/>
-    <mergeCell ref="D105:I105"/>
-    <mergeCell ref="D106:I106"/>
-    <mergeCell ref="D107:I107"/>
-    <mergeCell ref="D108:I108"/>
-    <mergeCell ref="D119:I119"/>
-    <mergeCell ref="D120:I120"/>
-    <mergeCell ref="D121:I121"/>
-    <mergeCell ref="D122:I122"/>
-    <mergeCell ref="D123:I123"/>
-    <mergeCell ref="D114:I114"/>
-    <mergeCell ref="D115:I115"/>
-    <mergeCell ref="D116:I116"/>
-    <mergeCell ref="D117:I117"/>
-    <mergeCell ref="D118:I118"/>
-    <mergeCell ref="D129:I129"/>
-    <mergeCell ref="D130:I130"/>
-    <mergeCell ref="D131:I131"/>
-    <mergeCell ref="D132:I132"/>
-    <mergeCell ref="D133:I133"/>
-    <mergeCell ref="D124:I124"/>
-    <mergeCell ref="D125:I125"/>
-    <mergeCell ref="D126:I126"/>
-    <mergeCell ref="D127:I127"/>
-    <mergeCell ref="D128:I128"/>
-    <mergeCell ref="D139:I139"/>
-    <mergeCell ref="D140:I140"/>
-    <mergeCell ref="D141:I141"/>
-    <mergeCell ref="D142:I142"/>
-    <mergeCell ref="D143:I143"/>
-    <mergeCell ref="D134:I134"/>
-    <mergeCell ref="D135:I135"/>
-    <mergeCell ref="D136:I136"/>
-    <mergeCell ref="D137:I137"/>
-    <mergeCell ref="D138:I138"/>
-    <mergeCell ref="D149:I149"/>
-    <mergeCell ref="D150:I150"/>
-    <mergeCell ref="D151:I151"/>
-    <mergeCell ref="D152:I152"/>
-    <mergeCell ref="D153:I153"/>
-    <mergeCell ref="D144:I144"/>
-    <mergeCell ref="D145:I145"/>
-    <mergeCell ref="D146:I146"/>
-    <mergeCell ref="D147:I147"/>
-    <mergeCell ref="D148:I148"/>
-    <mergeCell ref="D159:I159"/>
-    <mergeCell ref="D160:I160"/>
-    <mergeCell ref="D161:I161"/>
-    <mergeCell ref="D162:I162"/>
-    <mergeCell ref="D163:I163"/>
-    <mergeCell ref="D154:I154"/>
-    <mergeCell ref="D155:I155"/>
-    <mergeCell ref="D156:I156"/>
-    <mergeCell ref="D157:I157"/>
-    <mergeCell ref="D158:I158"/>
-    <mergeCell ref="D169:I169"/>
-    <mergeCell ref="D170:I170"/>
-    <mergeCell ref="D171:I171"/>
-    <mergeCell ref="D172:I172"/>
-    <mergeCell ref="D173:I173"/>
-    <mergeCell ref="D164:I164"/>
-    <mergeCell ref="D165:I165"/>
-    <mergeCell ref="D166:I166"/>
-    <mergeCell ref="D167:I167"/>
-    <mergeCell ref="D168:I168"/>
-    <mergeCell ref="D179:I179"/>
-    <mergeCell ref="D180:I180"/>
-    <mergeCell ref="D181:I181"/>
-    <mergeCell ref="D182:I182"/>
-    <mergeCell ref="D183:I183"/>
-    <mergeCell ref="D174:I174"/>
-    <mergeCell ref="D175:I175"/>
-    <mergeCell ref="D176:I176"/>
-    <mergeCell ref="D177:I177"/>
-    <mergeCell ref="D178:I178"/>
+    <mergeCell ref="B2:X2"/>
+    <mergeCell ref="M83"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="V7:X7"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="D83:I83"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="R7:T7"/>
+    <mergeCell ref="R6:T6"/>
+    <mergeCell ref="B4:X4"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B65:K65"/>
+    <mergeCell ref="L65:X65"/>
+    <mergeCell ref="V9:X9"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="O83"/>
+    <mergeCell ref="S83"/>
+    <mergeCell ref="B3:X3"/>
+    <mergeCell ref="U89:V89"/>
+    <mergeCell ref="K83"/>
+    <mergeCell ref="U83:V83"/>
+    <mergeCell ref="V8:X8"/>
+    <mergeCell ref="B29:K29"/>
+    <mergeCell ref="J9:L9"/>
+    <mergeCell ref="L29:X29"/>
+    <mergeCell ref="U84:V84"/>
+    <mergeCell ref="R9:T9"/>
+    <mergeCell ref="U87:V87"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="R8:T8"/>
+    <mergeCell ref="B48:K48"/>
+    <mergeCell ref="Q83"/>
+    <mergeCell ref="B11:K11"/>
+    <mergeCell ref="B83"/>
+    <mergeCell ref="D86:I86"/>
+    <mergeCell ref="D85:I85"/>
   </mergeCells>
   <conditionalFormatting sqref="K84:K183">
     <cfRule type="containsText" dxfId="22" priority="16" operator="containsText" text="Critical">
@@ -20761,8 +20814,9 @@
       <formula>AND($B84&lt;&gt;"",ISNUMBER($U84),$U84&lt;50)</formula>
     </cfRule>
   </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup scale="10" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="3.472222222222222E-3" right="3.472222222222222E-3" top="3.472222222222222E-3" bottom="3.472222222222222E-3" header="4.1666666666666666E-3" footer="4.1666666666666666E-3"/>
+  <pageSetup scale="10" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -30870,7 +30924,7 @@
         <v>9</v>
       </c>
       <c r="F2" s="26">
-        <f>ROUND(C2/B2*100,1)</f>
+        <f t="shared" ref="F2:F9" si="0">ROUND(C2/B2*100,1)</f>
         <v>75.5</v>
       </c>
     </row>
@@ -30891,7 +30945,7 @@
         <v>11</v>
       </c>
       <c r="F3" s="27">
-        <f>ROUND(C3/B3*100,1)</f>
+        <f t="shared" si="0"/>
         <v>84.8</v>
       </c>
     </row>
@@ -30912,7 +30966,7 @@
         <v>8</v>
       </c>
       <c r="F4" s="26">
-        <f>ROUND(C4/B4*100,1)</f>
+        <f t="shared" si="0"/>
         <v>86.2</v>
       </c>
     </row>
@@ -30933,7 +30987,7 @@
         <v>10</v>
       </c>
       <c r="F5" s="27">
-        <f>ROUND(C5/B5*100,1)</f>
+        <f t="shared" si="0"/>
         <v>72.099999999999994</v>
       </c>
     </row>
@@ -30954,7 +31008,7 @@
         <v>8</v>
       </c>
       <c r="F6" s="26">
-        <f>ROUND(C6/B6*100,1)</f>
+        <f t="shared" si="0"/>
         <v>87.8</v>
       </c>
     </row>
@@ -30975,7 +31029,7 @@
         <v>12</v>
       </c>
       <c r="F7" s="27">
-        <f>ROUND(C7/B7*100,1)</f>
+        <f t="shared" si="0"/>
         <v>76.900000000000006</v>
       </c>
     </row>
@@ -30996,7 +31050,7 @@
         <v>7</v>
       </c>
       <c r="F8" s="26">
-        <f>ROUND(C8/B8*100,1)</f>
+        <f t="shared" si="0"/>
         <v>79.400000000000006</v>
       </c>
     </row>
@@ -31017,7 +31071,7 @@
         <v>12</v>
       </c>
       <c r="F9" s="27">
-        <f>ROUND(C9/B9*100,1)</f>
+        <f t="shared" si="0"/>
         <v>73.8</v>
       </c>
     </row>
@@ -31064,34 +31118,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="240" t="s">
+      <c r="A1" s="247" t="s">
         <v>471</v>
       </c>
-      <c r="B1" s="240"/>
-      <c r="C1" s="240"/>
-      <c r="D1" s="240"/>
-      <c r="E1" s="240"/>
-      <c r="F1" s="240"/>
-      <c r="G1" s="240"/>
-      <c r="H1" s="240"/>
-      <c r="I1" s="240"/>
-      <c r="J1" s="240"/>
-      <c r="K1" s="240"/>
-      <c r="L1" s="240"/>
-      <c r="M1" s="240"/>
-      <c r="N1" s="240"/>
-      <c r="O1" s="240"/>
-      <c r="P1" s="240"/>
-      <c r="Q1" s="240"/>
-      <c r="R1" s="240"/>
-      <c r="S1" s="240"/>
-      <c r="T1" s="240"/>
-      <c r="U1" s="240"/>
-      <c r="V1" s="240"/>
-      <c r="W1" s="240"/>
-      <c r="X1" s="240"/>
-      <c r="Y1" s="240"/>
-      <c r="Z1" s="240"/>
+      <c r="B1" s="247"/>
+      <c r="C1" s="247"/>
+      <c r="D1" s="247"/>
+      <c r="E1" s="247"/>
+      <c r="F1" s="247"/>
+      <c r="G1" s="247"/>
+      <c r="H1" s="247"/>
+      <c r="I1" s="247"/>
+      <c r="J1" s="247"/>
+      <c r="K1" s="247"/>
+      <c r="L1" s="247"/>
+      <c r="M1" s="247"/>
+      <c r="N1" s="247"/>
+      <c r="O1" s="247"/>
+      <c r="P1" s="247"/>
+      <c r="Q1" s="247"/>
+      <c r="R1" s="247"/>
+      <c r="S1" s="247"/>
+      <c r="T1" s="247"/>
+      <c r="U1" s="247"/>
+      <c r="V1" s="247"/>
+      <c r="W1" s="247"/>
+      <c r="X1" s="247"/>
+      <c r="Y1" s="247"/>
+      <c r="Z1" s="247"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="51" t="s">
@@ -31780,18 +31834,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="241" t="s">
+      <c r="A1" s="248" t="s">
         <v>460</v>
       </c>
-      <c r="B1" s="242"/>
-      <c r="C1" s="242"/>
-      <c r="D1" s="242"/>
-      <c r="E1" s="242"/>
-      <c r="F1" s="242"/>
-      <c r="G1" s="242"/>
-      <c r="H1" s="242"/>
-      <c r="I1" s="242"/>
-      <c r="J1" s="242"/>
+      <c r="B1" s="248"/>
+      <c r="C1" s="248"/>
+      <c r="D1" s="248"/>
+      <c r="E1" s="248"/>
+      <c r="F1" s="248"/>
+      <c r="G1" s="248"/>
+      <c r="H1" s="248"/>
+      <c r="I1" s="248"/>
+      <c r="J1" s="248"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
@@ -31824,19 +31878,19 @@
       <c r="S2" s="1"/>
     </row>
     <row r="3" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="243" t="str">
+      <c r="A3" s="249" t="str">
         <f>"Sprint 1–8  |  "&amp;(COUNTA('Bug Tracker'!A:A)-1)&amp;" Total Bugs  |  "&amp;COUNTA($L$6:$L$12)&amp;" Testers"</f>
         <v>Sprint 1–8  |  201 Total Bugs  |  7 Testers</v>
       </c>
-      <c r="B3" s="242"/>
-      <c r="C3" s="242"/>
-      <c r="D3" s="242"/>
-      <c r="E3" s="242"/>
-      <c r="F3" s="242"/>
-      <c r="G3" s="242"/>
-      <c r="H3" s="242"/>
-      <c r="I3" s="242"/>
-      <c r="J3" s="242"/>
+      <c r="B3" s="150"/>
+      <c r="C3" s="150"/>
+      <c r="D3" s="150"/>
+      <c r="E3" s="150"/>
+      <c r="F3" s="150"/>
+      <c r="G3" s="150"/>
+      <c r="H3" s="150"/>
+      <c r="I3" s="150"/>
+      <c r="J3" s="150"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
@@ -32965,23 +33019,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="244" t="s">
+      <c r="A1" s="149" t="s">
         <v>467</v>
       </c>
-      <c r="B1" s="242"/>
-      <c r="C1" s="242"/>
-      <c r="D1" s="242"/>
-      <c r="E1" s="242"/>
-      <c r="F1" s="242"/>
-      <c r="G1" s="242"/>
-      <c r="H1" s="242"/>
-      <c r="I1" s="242"/>
-      <c r="J1" s="242"/>
-      <c r="K1" s="242"/>
-      <c r="L1" s="242"/>
-      <c r="M1" s="242"/>
-      <c r="N1" s="242"/>
-      <c r="O1" s="242"/>
+      <c r="B1" s="150"/>
+      <c r="C1" s="150"/>
+      <c r="D1" s="150"/>
+      <c r="E1" s="150"/>
+      <c r="F1" s="150"/>
+      <c r="G1" s="150"/>
+      <c r="H1" s="150"/>
+      <c r="I1" s="150"/>
+      <c r="J1" s="150"/>
+      <c r="K1" s="150"/>
+      <c r="L1" s="150"/>
+      <c r="M1" s="150"/>
+      <c r="N1" s="150"/>
+      <c r="O1" s="150"/>
     </row>
     <row r="2" spans="1:15" ht="3.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="40"/>
